--- a/data/derived_outputs/post_rescued_nrc_630_codebook.xlsx
+++ b/data/derived_outputs/post_rescued_nrc_630_codebook.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="1386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="1280">
   <si>
     <t>word</t>
   </si>
@@ -25,7 +25,7 @@
     <t>frequency_21215</t>
   </si>
   <si>
-    <t>chinese_translation</t>
+    <t>english_translation</t>
   </si>
   <si>
     <t>category_and_emotion</t>
@@ -3781,397 +3781,79 @@
     <t>刺激快感</t>
   </si>
   <si>
-    <t>1a. 原生 NRC 8大情绪词</t>
-  </si>
-  <si>
-    <t>1b. 原生 NRC 极性词</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (respectful -&gt; respectful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (immaculate -&gt; immaculate)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (annoying -&gt; annoying)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (fuss -&gt; fuss)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (awful -&gt; awful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (awed -&gt; awed)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (bubbly -&gt; bubbly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (praise -&gt; praise)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (trustworthy -&gt; trustworthy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (satisfaction -&gt; satisfaction)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (ruined -&gt; ruined)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (proud -&gt; proud)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (marvellous -&gt; marvellous)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (intrusive -&gt; intrusive)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (glowing -&gt; glowing)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (frustrating -&gt; frustrating)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (bothered -&gt; bothered)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (authentic -&gt; authentic)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (tricky -&gt; tricky)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (worldly -&gt; worldly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (vibrant -&gt; vibrant)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (uneasy -&gt; uneasy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (precious -&gt; precious)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (safest -&gt; safest)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (responsible -&gt; responsible)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (pleasurable -&gt; pleasurable)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (apologetic -&gt; apologetic)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (bored -&gt; bored)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (soaking -&gt; soaking)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (stuffy -&gt; stuffy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (superbly -&gt; superbly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (wondrous -&gt; wondrous)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (satisfying -&gt; satisfying)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (wary -&gt; wary)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (trepidation -&gt; trepidation)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (surprising -&gt; surprising)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (superlative -&gt; superlative)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (sketchy -&gt; sketchy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (slick -&gt; slick)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (rewarding -&gt; rewarding)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (nervousness -&gt; nervousness)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (mad -&gt; mad)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (inviting -&gt; inviting)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (cheesy -&gt; cheesy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (admire -&gt; admire)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (mesmerized -&gt; mesmerized)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (unfortunate -&gt; unfortunate)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (stunningly -&gt; stunningly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (stunned -&gt; stunned)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (stability -&gt; stability)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (raving -&gt; raving)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (quaint -&gt; quaint)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (wonderfull -&gt; wonderful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (jealous -&gt; jealous)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (improving -&gt; improving)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (improvement -&gt; improvement)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (friendlier -&gt; friendlier)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (emotional -&gt; emotional)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (ecstatic -&gt; ecstatic)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (conscientious -&gt; conscientious)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (badly -&gt; badly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (unspoiled -&gt; unspoiled)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (terribly -&gt; terribly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (susceptible -&gt; susceptible)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (stuffed -&gt; stuffed)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (miserable -&gt; miserable)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (hassles -&gt; hassles)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (effortless -&gt; effortless)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (compliment -&gt; compliment)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (claustrophobia -&gt; claustrophobia)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (cheerfully -&gt; cheerfully)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (bummer -&gt; bummer)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (awkward -&gt; awkward)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (automatically -&gt; automatically)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (mindful -&gt; mindful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (yummy -&gt; yummy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (unstable -&gt; unstable)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (spoiled -&gt; spoiled)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (shocked -&gt; shocked)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (poorly -&gt; poorly)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (nerve -&gt; nerve)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (grace -&gt; grace)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (frustration -&gt; frustration)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (frightened -&gt; frightened)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (exhilaration -&gt; exhilaration)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (exhausted -&gt; exhausted)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (dissapointed -&gt; disappointed)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (cherished -&gt; cherish)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (annoyed -&gt; annoyed)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (strange -&gt; strange)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (reputable -&gt; reputable)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (ridiculous -&gt; ridiculous)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (rudely -&gt; rudely)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (serenity -&gt; serenity)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (relieved -&gt; relieved)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (suffered -&gt; suffered)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (unhappy -&gt; unhappy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (unpleasant -&gt; unpleasant)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (powerful -&gt; powerful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (worrying -&gt; worry)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (weird -&gt; weird)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (painful -&gt; painful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (panic -&gt; panic)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (laughter -&gt; laughter)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (hopeful -&gt; hopeful)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (hesitating -&gt; hesitating)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (gushing -&gt; gushing)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (exhilerating -&gt; exhilarating)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (enthusiastically -&gt; enthusiastically)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (curious -&gt; curious)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (confusion -&gt; confusion)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (classy -&gt; classy)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (captivated -&gt; captivated)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (alas -&gt; alas)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (reassurance -&gt; reassurance)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (inspirational -&gt; inspirational)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (jovial -&gt; jovial)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (precision -&gt; precision)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (gratitude -&gt; gratitude)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (relief -&gt; relief)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (sublime -&gt; sublime)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (timid -&gt; timid)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (warmest -&gt; warmest)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (hug -&gt; hug)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (amaze -&gt; amaze)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (frightening -&gt; frightening)</t>
-  </si>
-  <si>
-    <t>1c. 语法变形拯救词 (calmer -&gt; calmer)</t>
-  </si>
-  <si>
-    <t>2a. 网络口语极级形容词 (Class 2 Gap)</t>
-  </si>
-  <si>
-    <t>2b. 低空观光领域专有词 (Class 3 Gap)</t>
+    <t>2a. Class 2 Web 2.0 Colloquial Superlatives (128 Words)</t>
+  </si>
+  <si>
+    <t>1a. Directly Mapped to NRC 8-Emotions (286 Words)</t>
+  </si>
+  <si>
+    <t>1b. Directly Mapped to Polarity Only (72 Words)</t>
+  </si>
+  <si>
+    <t>2b. Class 3 Low-Altitude Domain Lexicon (17 Words)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (concerned -&gt; concern)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (lucked -&gt; lucky)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (worries -&gt; worry)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (surprises -&gt; surprise)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (wonderfull -&gt; wonderful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (dissapointed -&gt; disappointed)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (cherished -&gt; cherish)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (worrying -&gt; worry)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (suprise -&gt; surprise)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (marveled -&gt; marvel)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (hates -&gt; hate)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (hated -&gt; hate)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (suprised -&gt; surprised)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (regretting -&gt; regret)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (dreaded -&gt; dread)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (dreading -&gt; dread)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (horribly -&gt; horrible)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (scaring -&gt; scare)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (apprehensions -&gt; apprehension)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (aprehensive -&gt; apprehensive)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 Morphological Rescued (disappointingly -&gt; disappointed)</t>
   </si>
 </sst>
 </file>
@@ -4631,7 +4313,7 @@
         <v>640</v>
       </c>
       <c r="E6" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4648,7 +4330,7 @@
         <v>641</v>
       </c>
       <c r="E7" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4835,7 +4517,7 @@
         <v>652</v>
       </c>
       <c r="E18" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4886,7 +4568,7 @@
         <v>655</v>
       </c>
       <c r="E21" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4903,7 +4585,7 @@
         <v>656</v>
       </c>
       <c r="E22" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4937,7 +4619,7 @@
         <v>658</v>
       </c>
       <c r="E24" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4971,7 +4653,7 @@
         <v>660</v>
       </c>
       <c r="E26" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4988,7 +4670,7 @@
         <v>661</v>
       </c>
       <c r="E27" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5005,7 +4687,7 @@
         <v>662</v>
       </c>
       <c r="E28" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5022,7 +4704,7 @@
         <v>663</v>
       </c>
       <c r="E29" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5039,7 +4721,7 @@
         <v>664</v>
       </c>
       <c r="E30" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5056,7 +4738,7 @@
         <v>665</v>
       </c>
       <c r="E31" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5073,7 +4755,7 @@
         <v>666</v>
       </c>
       <c r="E32" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5175,7 +4857,7 @@
         <v>672</v>
       </c>
       <c r="E38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5226,7 +4908,7 @@
         <v>675</v>
       </c>
       <c r="E41" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5311,7 +4993,7 @@
         <v>680</v>
       </c>
       <c r="E46" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -5328,7 +5010,7 @@
         <v>681</v>
       </c>
       <c r="E47" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5413,7 +5095,7 @@
         <v>686</v>
       </c>
       <c r="E52" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5447,7 +5129,7 @@
         <v>688</v>
       </c>
       <c r="E54" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -5498,7 +5180,7 @@
         <v>691</v>
       </c>
       <c r="E57" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -5549,7 +5231,7 @@
         <v>694</v>
       </c>
       <c r="E60" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -5566,7 +5248,7 @@
         <v>695</v>
       </c>
       <c r="E61" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -5600,7 +5282,7 @@
         <v>697</v>
       </c>
       <c r="E63" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5685,7 +5367,7 @@
         <v>702</v>
       </c>
       <c r="E68" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -5702,7 +5384,7 @@
         <v>703</v>
       </c>
       <c r="E69" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -5787,7 +5469,7 @@
         <v>708</v>
       </c>
       <c r="E74" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -5804,7 +5486,7 @@
         <v>709</v>
       </c>
       <c r="E75" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -5838,7 +5520,7 @@
         <v>711</v>
       </c>
       <c r="E77" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -5855,7 +5537,7 @@
         <v>712</v>
       </c>
       <c r="E78" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -5889,7 +5571,7 @@
         <v>714</v>
       </c>
       <c r="E80" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -5923,7 +5605,7 @@
         <v>716</v>
       </c>
       <c r="E82" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -5940,7 +5622,7 @@
         <v>717</v>
       </c>
       <c r="E83" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -5974,7 +5656,7 @@
         <v>719</v>
       </c>
       <c r="E85" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5991,7 +5673,7 @@
         <v>720</v>
       </c>
       <c r="E86" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -6008,7 +5690,7 @@
         <v>716</v>
       </c>
       <c r="E87" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -6059,7 +5741,7 @@
         <v>723</v>
       </c>
       <c r="E90" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -6076,7 +5758,7 @@
         <v>724</v>
       </c>
       <c r="E91" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -6093,7 +5775,7 @@
         <v>725</v>
       </c>
       <c r="E92" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -6110,7 +5792,7 @@
         <v>726</v>
       </c>
       <c r="E93" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -6195,7 +5877,7 @@
         <v>731</v>
       </c>
       <c r="E98" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -6212,7 +5894,7 @@
         <v>732</v>
       </c>
       <c r="E99" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -6297,7 +5979,7 @@
         <v>737</v>
       </c>
       <c r="E104" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -6314,7 +5996,7 @@
         <v>738</v>
       </c>
       <c r="E105" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -6365,7 +6047,7 @@
         <v>741</v>
       </c>
       <c r="E108" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -6382,7 +6064,7 @@
         <v>742</v>
       </c>
       <c r="E109" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -6416,7 +6098,7 @@
         <v>744</v>
       </c>
       <c r="E111" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -6433,7 +6115,7 @@
         <v>745</v>
       </c>
       <c r="E112" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -6450,7 +6132,7 @@
         <v>746</v>
       </c>
       <c r="E113" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -6484,7 +6166,7 @@
         <v>748</v>
       </c>
       <c r="E115" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -6518,7 +6200,7 @@
         <v>750</v>
       </c>
       <c r="E117" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -6569,7 +6251,7 @@
         <v>753</v>
       </c>
       <c r="E120" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -6603,7 +6285,7 @@
         <v>755</v>
       </c>
       <c r="E122" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -6705,7 +6387,7 @@
         <v>761</v>
       </c>
       <c r="E128" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -6739,7 +6421,7 @@
         <v>763</v>
       </c>
       <c r="E130" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -6756,7 +6438,7 @@
         <v>764</v>
       </c>
       <c r="E131" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6773,7 +6455,7 @@
         <v>765</v>
       </c>
       <c r="E132" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6875,7 +6557,7 @@
         <v>771</v>
       </c>
       <c r="E138" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -6892,7 +6574,7 @@
         <v>772</v>
       </c>
       <c r="E139" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -6909,7 +6591,7 @@
         <v>773</v>
       </c>
       <c r="E140" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -6926,7 +6608,7 @@
         <v>774</v>
       </c>
       <c r="E141" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -6943,7 +6625,7 @@
         <v>775</v>
       </c>
       <c r="E142" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -6960,7 +6642,7 @@
         <v>776</v>
       </c>
       <c r="E143" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -6977,7 +6659,7 @@
         <v>777</v>
       </c>
       <c r="E144" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7062,7 +6744,7 @@
         <v>782</v>
       </c>
       <c r="E149" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7147,7 +6829,7 @@
         <v>787</v>
       </c>
       <c r="E154" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7164,7 +6846,7 @@
         <v>788</v>
       </c>
       <c r="E155" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7181,7 +6863,7 @@
         <v>789</v>
       </c>
       <c r="E156" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7215,7 +6897,7 @@
         <v>791</v>
       </c>
       <c r="E158" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7266,7 +6948,7 @@
         <v>794</v>
       </c>
       <c r="E161" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -7300,7 +6982,7 @@
         <v>796</v>
       </c>
       <c r="E163" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -7317,7 +6999,7 @@
         <v>797</v>
       </c>
       <c r="E164" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -7351,7 +7033,7 @@
         <v>799</v>
       </c>
       <c r="E166" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -7368,7 +7050,7 @@
         <v>800</v>
       </c>
       <c r="E167" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -7385,7 +7067,7 @@
         <v>801</v>
       </c>
       <c r="E168" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -7402,7 +7084,7 @@
         <v>802</v>
       </c>
       <c r="E169" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -7453,7 +7135,7 @@
         <v>805</v>
       </c>
       <c r="E172" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -7470,7 +7152,7 @@
         <v>806</v>
       </c>
       <c r="E173" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -7555,7 +7237,7 @@
         <v>811</v>
       </c>
       <c r="E178" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -7572,7 +7254,7 @@
         <v>812</v>
       </c>
       <c r="E179" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -7589,7 +7271,7 @@
         <v>813</v>
       </c>
       <c r="E180" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -7606,7 +7288,7 @@
         <v>772</v>
       </c>
       <c r="E181" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -7623,7 +7305,7 @@
         <v>814</v>
       </c>
       <c r="E182" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -7657,7 +7339,7 @@
         <v>816</v>
       </c>
       <c r="E184" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -7674,7 +7356,7 @@
         <v>817</v>
       </c>
       <c r="E185" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -7691,7 +7373,7 @@
         <v>818</v>
       </c>
       <c r="E186" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -7708,7 +7390,7 @@
         <v>819</v>
       </c>
       <c r="E187" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -7725,7 +7407,7 @@
         <v>820</v>
       </c>
       <c r="E188" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -7742,7 +7424,7 @@
         <v>821</v>
       </c>
       <c r="E189" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -7776,7 +7458,7 @@
         <v>823</v>
       </c>
       <c r="E191" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -7793,7 +7475,7 @@
         <v>824</v>
       </c>
       <c r="E192" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -7861,7 +7543,7 @@
         <v>828</v>
       </c>
       <c r="E196" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -7963,7 +7645,7 @@
         <v>727</v>
       </c>
       <c r="E202" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -7980,7 +7662,7 @@
         <v>834</v>
       </c>
       <c r="E203" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -8014,7 +7696,7 @@
         <v>836</v>
       </c>
       <c r="E205" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -8065,7 +7747,7 @@
         <v>839</v>
       </c>
       <c r="E208" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -8116,7 +7798,7 @@
         <v>842</v>
       </c>
       <c r="E211" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -8133,7 +7815,7 @@
         <v>843</v>
       </c>
       <c r="E212" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -8218,7 +7900,7 @@
         <v>848</v>
       </c>
       <c r="E217" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -8286,7 +7968,7 @@
         <v>852</v>
       </c>
       <c r="E221" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -8303,7 +7985,7 @@
         <v>853</v>
       </c>
       <c r="E222" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -8320,7 +8002,7 @@
         <v>854</v>
       </c>
       <c r="E223" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -8337,7 +8019,7 @@
         <v>855</v>
       </c>
       <c r="E224" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -8371,7 +8053,7 @@
         <v>857</v>
       </c>
       <c r="E226" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -8439,7 +8121,7 @@
         <v>861</v>
       </c>
       <c r="E230" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -8490,7 +8172,7 @@
         <v>864</v>
       </c>
       <c r="E233" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -8507,7 +8189,7 @@
         <v>865</v>
       </c>
       <c r="E234" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -8524,7 +8206,7 @@
         <v>866</v>
       </c>
       <c r="E235" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -8592,7 +8274,7 @@
         <v>870</v>
       </c>
       <c r="E239" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -8609,7 +8291,7 @@
         <v>871</v>
       </c>
       <c r="E240" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -8626,7 +8308,7 @@
         <v>872</v>
       </c>
       <c r="E241" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -8643,7 +8325,7 @@
         <v>873</v>
       </c>
       <c r="E242" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -8677,7 +8359,7 @@
         <v>874</v>
       </c>
       <c r="E244" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -8694,7 +8376,7 @@
         <v>875</v>
       </c>
       <c r="E245" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -8711,7 +8393,7 @@
         <v>876</v>
       </c>
       <c r="E246" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -8728,7 +8410,7 @@
         <v>682</v>
       </c>
       <c r="E247" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -8745,7 +8427,7 @@
         <v>877</v>
       </c>
       <c r="E248" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -8762,7 +8444,7 @@
         <v>878</v>
       </c>
       <c r="E249" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -8779,7 +8461,7 @@
         <v>879</v>
       </c>
       <c r="E250" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -8796,7 +8478,7 @@
         <v>880</v>
       </c>
       <c r="E251" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -8813,7 +8495,7 @@
         <v>881</v>
       </c>
       <c r="E252" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -8830,7 +8512,7 @@
         <v>882</v>
       </c>
       <c r="E253" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -8847,7 +8529,7 @@
         <v>883</v>
       </c>
       <c r="E254" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -8864,7 +8546,7 @@
         <v>884</v>
       </c>
       <c r="E255" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -8898,7 +8580,7 @@
         <v>886</v>
       </c>
       <c r="E257" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -8915,7 +8597,7 @@
         <v>887</v>
       </c>
       <c r="E258" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -8949,7 +8631,7 @@
         <v>889</v>
       </c>
       <c r="E260" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -8983,7 +8665,7 @@
         <v>891</v>
       </c>
       <c r="E262" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -9017,7 +8699,7 @@
         <v>893</v>
       </c>
       <c r="E264" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -9068,7 +8750,7 @@
         <v>896</v>
       </c>
       <c r="E267" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -9119,7 +8801,7 @@
         <v>899</v>
       </c>
       <c r="E270" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -9136,7 +8818,7 @@
         <v>900</v>
       </c>
       <c r="E271" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -9153,7 +8835,7 @@
         <v>901</v>
       </c>
       <c r="E272" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -9221,7 +8903,7 @@
         <v>905</v>
       </c>
       <c r="E276" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -9238,7 +8920,7 @@
         <v>906</v>
       </c>
       <c r="E277" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -9255,7 +8937,7 @@
         <v>907</v>
       </c>
       <c r="E278" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -9306,7 +8988,7 @@
         <v>909</v>
       </c>
       <c r="E281" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -9340,7 +9022,7 @@
         <v>911</v>
       </c>
       <c r="E283" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -9374,7 +9056,7 @@
         <v>913</v>
       </c>
       <c r="E285" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -9391,7 +9073,7 @@
         <v>914</v>
       </c>
       <c r="E286" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -9408,7 +9090,7 @@
         <v>915</v>
       </c>
       <c r="E287" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -9425,7 +9107,7 @@
         <v>916</v>
       </c>
       <c r="E288" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -9442,7 +9124,7 @@
         <v>917</v>
       </c>
       <c r="E289" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -9459,7 +9141,7 @@
         <v>918</v>
       </c>
       <c r="E290" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -9527,7 +9209,7 @@
         <v>922</v>
       </c>
       <c r="E294" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -9578,7 +9260,7 @@
         <v>901</v>
       </c>
       <c r="E297" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -9595,7 +9277,7 @@
         <v>925</v>
       </c>
       <c r="E298" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -9629,7 +9311,7 @@
         <v>927</v>
       </c>
       <c r="E300" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -9646,7 +9328,7 @@
         <v>928</v>
       </c>
       <c r="E301" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -9663,7 +9345,7 @@
         <v>929</v>
       </c>
       <c r="E302" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -9697,7 +9379,7 @@
         <v>931</v>
       </c>
       <c r="E304" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -9731,7 +9413,7 @@
         <v>933</v>
       </c>
       <c r="E306" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -9748,7 +9430,7 @@
         <v>934</v>
       </c>
       <c r="E307" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -9765,7 +9447,7 @@
         <v>935</v>
       </c>
       <c r="E308" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -9782,7 +9464,7 @@
         <v>936</v>
       </c>
       <c r="E309" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -9816,7 +9498,7 @@
         <v>938</v>
       </c>
       <c r="E311" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -9833,7 +9515,7 @@
         <v>939</v>
       </c>
       <c r="E312" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -9867,7 +9549,7 @@
         <v>941</v>
       </c>
       <c r="E314" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -9884,7 +9566,7 @@
         <v>942</v>
       </c>
       <c r="E315" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -9935,7 +9617,7 @@
         <v>945</v>
       </c>
       <c r="E318" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -9969,7 +9651,7 @@
         <v>947</v>
       </c>
       <c r="E320" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -10003,7 +9685,7 @@
         <v>949</v>
       </c>
       <c r="E322" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -10020,7 +9702,7 @@
         <v>950</v>
       </c>
       <c r="E323" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -10037,7 +9719,7 @@
         <v>951</v>
       </c>
       <c r="E324" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -10054,7 +9736,7 @@
         <v>952</v>
       </c>
       <c r="E325" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -10071,7 +9753,7 @@
         <v>953</v>
       </c>
       <c r="E326" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -10088,7 +9770,7 @@
         <v>954</v>
       </c>
       <c r="E327" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -10173,7 +9855,7 @@
         <v>959</v>
       </c>
       <c r="E332" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -10207,7 +9889,7 @@
         <v>961</v>
       </c>
       <c r="E334" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -10224,7 +9906,7 @@
         <v>962</v>
       </c>
       <c r="E335" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -10241,7 +9923,7 @@
         <v>963</v>
       </c>
       <c r="E336" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -10275,7 +9957,7 @@
         <v>965</v>
       </c>
       <c r="E338" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -10292,7 +9974,7 @@
         <v>966</v>
       </c>
       <c r="E339" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -10309,7 +9991,7 @@
         <v>967</v>
       </c>
       <c r="E340" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -10326,7 +10008,7 @@
         <v>968</v>
       </c>
       <c r="E341" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -10360,7 +10042,7 @@
         <v>830</v>
       </c>
       <c r="E343" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -10394,7 +10076,7 @@
         <v>971</v>
       </c>
       <c r="E345" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -10411,7 +10093,7 @@
         <v>972</v>
       </c>
       <c r="E346" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -10445,7 +10127,7 @@
         <v>974</v>
       </c>
       <c r="E348" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -10462,7 +10144,7 @@
         <v>975</v>
       </c>
       <c r="E349" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -10615,7 +10297,7 @@
         <v>984</v>
       </c>
       <c r="E358" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -10632,7 +10314,7 @@
         <v>985</v>
       </c>
       <c r="E359" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -10649,7 +10331,7 @@
         <v>986</v>
       </c>
       <c r="E360" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -10666,7 +10348,7 @@
         <v>987</v>
       </c>
       <c r="E361" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -10683,7 +10365,7 @@
         <v>988</v>
       </c>
       <c r="E362" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -10700,7 +10382,7 @@
         <v>989</v>
       </c>
       <c r="E363" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -10717,7 +10399,7 @@
         <v>990</v>
       </c>
       <c r="E364" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -10734,7 +10416,7 @@
         <v>991</v>
       </c>
       <c r="E365" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -10751,7 +10433,7 @@
         <v>992</v>
       </c>
       <c r="E366" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -10768,7 +10450,7 @@
         <v>993</v>
       </c>
       <c r="E367" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -10785,7 +10467,7 @@
         <v>994</v>
       </c>
       <c r="E368" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -10802,7 +10484,7 @@
         <v>995</v>
       </c>
       <c r="E369" t="s">
-        <v>1266</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -10819,7 +10501,7 @@
         <v>996</v>
       </c>
       <c r="E370" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -10836,7 +10518,7 @@
         <v>997</v>
       </c>
       <c r="E371" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -10853,7 +10535,7 @@
         <v>998</v>
       </c>
       <c r="E372" t="s">
-        <v>1269</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -10870,7 +10552,7 @@
         <v>999</v>
       </c>
       <c r="E373" t="s">
-        <v>1270</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -10887,7 +10569,7 @@
         <v>1000</v>
       </c>
       <c r="E374" t="s">
-        <v>1271</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -10904,7 +10586,7 @@
         <v>1001</v>
       </c>
       <c r="E375" t="s">
-        <v>1272</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -10921,7 +10603,7 @@
         <v>1002</v>
       </c>
       <c r="E376" t="s">
-        <v>1273</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -10938,7 +10620,7 @@
         <v>1003</v>
       </c>
       <c r="E377" t="s">
-        <v>1274</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -10955,7 +10637,7 @@
         <v>1004</v>
       </c>
       <c r="E378" t="s">
-        <v>1275</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -10972,7 +10654,7 @@
         <v>1005</v>
       </c>
       <c r="E379" t="s">
-        <v>1276</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -10989,7 +10671,7 @@
         <v>1006</v>
       </c>
       <c r="E380" t="s">
-        <v>1277</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -11006,7 +10688,7 @@
         <v>1007</v>
       </c>
       <c r="E381" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -11023,7 +10705,7 @@
         <v>1008</v>
       </c>
       <c r="E382" t="s">
-        <v>1279</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -11040,7 +10722,7 @@
         <v>1009</v>
       </c>
       <c r="E383" t="s">
-        <v>1280</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -11057,7 +10739,7 @@
         <v>1010</v>
       </c>
       <c r="E384" t="s">
-        <v>1281</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -11074,7 +10756,7 @@
         <v>1011</v>
       </c>
       <c r="E385" t="s">
-        <v>1282</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -11091,7 +10773,7 @@
         <v>1012</v>
       </c>
       <c r="E386" t="s">
-        <v>1283</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -11108,7 +10790,7 @@
         <v>1013</v>
       </c>
       <c r="E387" t="s">
-        <v>1284</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -11125,7 +10807,7 @@
         <v>1014</v>
       </c>
       <c r="E388" t="s">
-        <v>1285</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -11142,7 +10824,7 @@
         <v>1015</v>
       </c>
       <c r="E389" t="s">
-        <v>1286</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -11159,7 +10841,7 @@
         <v>1016</v>
       </c>
       <c r="E390" t="s">
-        <v>1287</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -11176,7 +10858,7 @@
         <v>1017</v>
       </c>
       <c r="E391" t="s">
-        <v>1288</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -11193,7 +10875,7 @@
         <v>1018</v>
       </c>
       <c r="E392" t="s">
-        <v>1289</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -11210,7 +10892,7 @@
         <v>1019</v>
       </c>
       <c r="E393" t="s">
-        <v>1290</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -11227,7 +10909,7 @@
         <v>1020</v>
       </c>
       <c r="E394" t="s">
-        <v>1291</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -11244,7 +10926,7 @@
         <v>1021</v>
       </c>
       <c r="E395" t="s">
-        <v>1292</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -11261,7 +10943,7 @@
         <v>1022</v>
       </c>
       <c r="E396" t="s">
-        <v>1293</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -11278,7 +10960,7 @@
         <v>1023</v>
       </c>
       <c r="E397" t="s">
-        <v>1294</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -11295,7 +10977,7 @@
         <v>1024</v>
       </c>
       <c r="E398" t="s">
-        <v>1295</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -11312,7 +10994,7 @@
         <v>1025</v>
       </c>
       <c r="E399" t="s">
-        <v>1296</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -11329,7 +11011,7 @@
         <v>1026</v>
       </c>
       <c r="E400" t="s">
-        <v>1297</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -11346,7 +11028,7 @@
         <v>1027</v>
       </c>
       <c r="E401" t="s">
-        <v>1298</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -11363,7 +11045,7 @@
         <v>1028</v>
       </c>
       <c r="E402" t="s">
-        <v>1299</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -11380,7 +11062,7 @@
         <v>1029</v>
       </c>
       <c r="E403" t="s">
-        <v>1300</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -11397,7 +11079,7 @@
         <v>1030</v>
       </c>
       <c r="E404" t="s">
-        <v>1301</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -11414,7 +11096,7 @@
         <v>1031</v>
       </c>
       <c r="E405" t="s">
-        <v>1302</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -11431,7 +11113,7 @@
         <v>1032</v>
       </c>
       <c r="E406" t="s">
-        <v>1303</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -11448,7 +11130,7 @@
         <v>1033</v>
       </c>
       <c r="E407" t="s">
-        <v>1304</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -11465,7 +11147,7 @@
         <v>1034</v>
       </c>
       <c r="E408" t="s">
-        <v>1305</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -11482,7 +11164,7 @@
         <v>1035</v>
       </c>
       <c r="E409" t="s">
-        <v>1306</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -11499,7 +11181,7 @@
         <v>1036</v>
       </c>
       <c r="E410" t="s">
-        <v>1307</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -11516,7 +11198,7 @@
         <v>1037</v>
       </c>
       <c r="E411" t="s">
-        <v>1308</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -11533,7 +11215,7 @@
         <v>1038</v>
       </c>
       <c r="E412" t="s">
-        <v>1309</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -11550,7 +11232,7 @@
         <v>1039</v>
       </c>
       <c r="E413" t="s">
-        <v>1310</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -11567,7 +11249,7 @@
         <v>1040</v>
       </c>
       <c r="E414" t="s">
-        <v>1311</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -11584,7 +11266,7 @@
         <v>1041</v>
       </c>
       <c r="E415" t="s">
-        <v>1312</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -11601,7 +11283,7 @@
         <v>1042</v>
       </c>
       <c r="E416" t="s">
-        <v>1313</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -11618,7 +11300,7 @@
         <v>1043</v>
       </c>
       <c r="E417" t="s">
-        <v>1314</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -11635,7 +11317,7 @@
         <v>1044</v>
       </c>
       <c r="E418" t="s">
-        <v>1315</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -11652,7 +11334,7 @@
         <v>1045</v>
       </c>
       <c r="E419" t="s">
-        <v>1316</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -11669,7 +11351,7 @@
         <v>1046</v>
       </c>
       <c r="E420" t="s">
-        <v>1317</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -11686,7 +11368,7 @@
         <v>1047</v>
       </c>
       <c r="E421" t="s">
-        <v>1318</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -11703,7 +11385,7 @@
         <v>1048</v>
       </c>
       <c r="E422" t="s">
-        <v>1319</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -11720,7 +11402,7 @@
         <v>1049</v>
       </c>
       <c r="E423" t="s">
-        <v>1320</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -11737,7 +11419,7 @@
         <v>1050</v>
       </c>
       <c r="E424" t="s">
-        <v>1321</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -11754,7 +11436,7 @@
         <v>1051</v>
       </c>
       <c r="E425" t="s">
-        <v>1322</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -11771,7 +11453,7 @@
         <v>1052</v>
       </c>
       <c r="E426" t="s">
-        <v>1323</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -11788,7 +11470,7 @@
         <v>1053</v>
       </c>
       <c r="E427" t="s">
-        <v>1324</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -11805,7 +11487,7 @@
         <v>1054</v>
       </c>
       <c r="E428" t="s">
-        <v>1325</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -11822,7 +11504,7 @@
         <v>1055</v>
       </c>
       <c r="E429" t="s">
-        <v>1326</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -11839,7 +11521,7 @@
         <v>1056</v>
       </c>
       <c r="E430" t="s">
-        <v>1327</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -11856,7 +11538,7 @@
         <v>1057</v>
       </c>
       <c r="E431" t="s">
-        <v>1328</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -11873,7 +11555,7 @@
         <v>1058</v>
       </c>
       <c r="E432" t="s">
-        <v>1329</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -11890,7 +11572,7 @@
         <v>1059</v>
       </c>
       <c r="E433" t="s">
-        <v>1330</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -11907,7 +11589,7 @@
         <v>1060</v>
       </c>
       <c r="E434" t="s">
-        <v>1331</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -11924,7 +11606,7 @@
         <v>870</v>
       </c>
       <c r="E435" t="s">
-        <v>1332</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -11941,7 +11623,7 @@
         <v>1061</v>
       </c>
       <c r="E436" t="s">
-        <v>1333</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -11958,7 +11640,7 @@
         <v>1062</v>
       </c>
       <c r="E437" t="s">
-        <v>1334</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -11975,7 +11657,7 @@
         <v>1063</v>
       </c>
       <c r="E438" t="s">
-        <v>1335</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -11992,7 +11674,7 @@
         <v>1064</v>
       </c>
       <c r="E439" t="s">
-        <v>1336</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -12009,7 +11691,7 @@
         <v>1065</v>
       </c>
       <c r="E440" t="s">
-        <v>1337</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -12026,7 +11708,7 @@
         <v>1066</v>
       </c>
       <c r="E441" t="s">
-        <v>1338</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -12043,7 +11725,7 @@
         <v>1067</v>
       </c>
       <c r="E442" t="s">
-        <v>1339</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -12060,7 +11742,7 @@
         <v>1068</v>
       </c>
       <c r="E443" t="s">
-        <v>1340</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -12077,7 +11759,7 @@
         <v>1069</v>
       </c>
       <c r="E444" t="s">
-        <v>1341</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -12094,7 +11776,7 @@
         <v>1070</v>
       </c>
       <c r="E445" t="s">
-        <v>1342</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -12111,7 +11793,7 @@
         <v>1071</v>
       </c>
       <c r="E446" t="s">
-        <v>1343</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -12128,7 +11810,7 @@
         <v>1072</v>
       </c>
       <c r="E447" t="s">
-        <v>1344</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -12145,7 +11827,7 @@
         <v>1073</v>
       </c>
       <c r="E448" t="s">
-        <v>1345</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -12162,7 +11844,7 @@
         <v>1074</v>
       </c>
       <c r="E449" t="s">
-        <v>1346</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -12179,7 +11861,7 @@
         <v>1075</v>
       </c>
       <c r="E450" t="s">
-        <v>1347</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -12196,7 +11878,7 @@
         <v>1076</v>
       </c>
       <c r="E451" t="s">
-        <v>1348</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -12213,7 +11895,7 @@
         <v>1077</v>
       </c>
       <c r="E452" t="s">
-        <v>1349</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -12230,7 +11912,7 @@
         <v>1078</v>
       </c>
       <c r="E453" t="s">
-        <v>1350</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -12247,7 +11929,7 @@
         <v>1079</v>
       </c>
       <c r="E454" t="s">
-        <v>1351</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -12264,7 +11946,7 @@
         <v>1080</v>
       </c>
       <c r="E455" t="s">
-        <v>1352</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -12281,7 +11963,7 @@
         <v>1081</v>
       </c>
       <c r="E456" t="s">
-        <v>1353</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -12298,7 +11980,7 @@
         <v>1082</v>
       </c>
       <c r="E457" t="s">
-        <v>1354</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -12315,7 +11997,7 @@
         <v>1083</v>
       </c>
       <c r="E458" t="s">
-        <v>1355</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -12332,7 +12014,7 @@
         <v>1084</v>
       </c>
       <c r="E459" t="s">
-        <v>1356</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -12349,7 +12031,7 @@
         <v>1085</v>
       </c>
       <c r="E460" t="s">
-        <v>1357</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -12366,7 +12048,7 @@
         <v>1086</v>
       </c>
       <c r="E461" t="s">
-        <v>1358</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -12383,7 +12065,7 @@
         <v>1087</v>
       </c>
       <c r="E462" t="s">
-        <v>1359</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -12400,7 +12082,7 @@
         <v>1088</v>
       </c>
       <c r="E463" t="s">
-        <v>1360</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -12417,7 +12099,7 @@
         <v>1089</v>
       </c>
       <c r="E464" t="s">
-        <v>1361</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -12434,7 +12116,7 @@
         <v>1090</v>
       </c>
       <c r="E465" t="s">
-        <v>1362</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -12451,7 +12133,7 @@
         <v>1091</v>
       </c>
       <c r="E466" t="s">
-        <v>1363</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -12468,7 +12150,7 @@
         <v>1092</v>
       </c>
       <c r="E467" t="s">
-        <v>1364</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -12485,7 +12167,7 @@
         <v>1093</v>
       </c>
       <c r="E468" t="s">
-        <v>1365</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -12502,7 +12184,7 @@
         <v>1094</v>
       </c>
       <c r="E469" t="s">
-        <v>1366</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -12519,7 +12201,7 @@
         <v>1095</v>
       </c>
       <c r="E470" t="s">
-        <v>1367</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -12536,7 +12218,7 @@
         <v>1096</v>
       </c>
       <c r="E471" t="s">
-        <v>1368</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -12553,7 +12235,7 @@
         <v>1097</v>
       </c>
       <c r="E472" t="s">
-        <v>1369</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -12570,7 +12252,7 @@
         <v>1098</v>
       </c>
       <c r="E473" t="s">
-        <v>1370</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -12587,7 +12269,7 @@
         <v>1099</v>
       </c>
       <c r="E474" t="s">
-        <v>1371</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -12604,7 +12286,7 @@
         <v>1100</v>
       </c>
       <c r="E475" t="s">
-        <v>1372</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -12621,7 +12303,7 @@
         <v>1101</v>
       </c>
       <c r="E476" t="s">
-        <v>1373</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -12638,7 +12320,7 @@
         <v>1102</v>
       </c>
       <c r="E477" t="s">
-        <v>1374</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -12655,7 +12337,7 @@
         <v>1103</v>
       </c>
       <c r="E478" t="s">
-        <v>1375</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -12672,7 +12354,7 @@
         <v>1104</v>
       </c>
       <c r="E479" t="s">
-        <v>1376</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -12689,7 +12371,7 @@
         <v>1105</v>
       </c>
       <c r="E480" t="s">
-        <v>1377</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -12706,7 +12388,7 @@
         <v>1106</v>
       </c>
       <c r="E481" t="s">
-        <v>1378</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -12723,7 +12405,7 @@
         <v>1107</v>
       </c>
       <c r="E482" t="s">
-        <v>1379</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -12740,7 +12422,7 @@
         <v>1108</v>
       </c>
       <c r="E483" t="s">
-        <v>1380</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -12757,7 +12439,7 @@
         <v>1109</v>
       </c>
       <c r="E484" t="s">
-        <v>1381</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -12774,7 +12456,7 @@
         <v>1110</v>
       </c>
       <c r="E485" t="s">
-        <v>1382</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -12791,7 +12473,7 @@
         <v>1111</v>
       </c>
       <c r="E486" t="s">
-        <v>1383</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -12808,7 +12490,7 @@
         <v>1112</v>
       </c>
       <c r="E487" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -12825,7 +12507,7 @@
         <v>1113</v>
       </c>
       <c r="E488" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -12842,7 +12524,7 @@
         <v>1114</v>
       </c>
       <c r="E489" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -12859,7 +12541,7 @@
         <v>1115</v>
       </c>
       <c r="E490" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -12876,7 +12558,7 @@
         <v>1116</v>
       </c>
       <c r="E491" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -12893,7 +12575,7 @@
         <v>1117</v>
       </c>
       <c r="E492" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -12910,7 +12592,7 @@
         <v>1031</v>
       </c>
       <c r="E493" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -12927,7 +12609,7 @@
         <v>1118</v>
       </c>
       <c r="E494" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -12944,7 +12626,7 @@
         <v>1119</v>
       </c>
       <c r="E495" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -12961,7 +12643,7 @@
         <v>1120</v>
       </c>
       <c r="E496" t="s">
-        <v>1384</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -12978,7 +12660,7 @@
         <v>1121</v>
       </c>
       <c r="E497" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -12995,7 +12677,7 @@
         <v>1122</v>
       </c>
       <c r="E498" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -13012,7 +12694,7 @@
         <v>1123</v>
       </c>
       <c r="E499" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -13029,7 +12711,7 @@
         <v>1124</v>
       </c>
       <c r="E500" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -13046,7 +12728,7 @@
         <v>1125</v>
       </c>
       <c r="E501" t="s">
-        <v>1384</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="502" spans="1:5">
@@ -13063,7 +12745,7 @@
         <v>1126</v>
       </c>
       <c r="E502" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -13080,7 +12762,7 @@
         <v>1127</v>
       </c>
       <c r="E503" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -13097,7 +12779,7 @@
         <v>1128</v>
       </c>
       <c r="E504" t="s">
-        <v>1384</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="505" spans="1:5">
@@ -13114,7 +12796,7 @@
         <v>1129</v>
       </c>
       <c r="E505" t="s">
-        <v>1384</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -13131,7 +12813,7 @@
         <v>1130</v>
       </c>
       <c r="E506" t="s">
-        <v>1384</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -13148,7 +12830,7 @@
         <v>1131</v>
       </c>
       <c r="E507" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -13165,7 +12847,7 @@
         <v>1132</v>
       </c>
       <c r="E508" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -13182,7 +12864,7 @@
         <v>1133</v>
       </c>
       <c r="E509" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -13199,7 +12881,7 @@
         <v>1134</v>
       </c>
       <c r="E510" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -13216,7 +12898,7 @@
         <v>1135</v>
       </c>
       <c r="E511" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -13233,7 +12915,7 @@
         <v>1136</v>
       </c>
       <c r="E512" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -13250,7 +12932,7 @@
         <v>1137</v>
       </c>
       <c r="E513" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -13267,7 +12949,7 @@
         <v>1138</v>
       </c>
       <c r="E514" t="s">
-        <v>1384</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -13284,7 +12966,7 @@
         <v>1139</v>
       </c>
       <c r="E515" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -13301,7 +12983,7 @@
         <v>1140</v>
       </c>
       <c r="E516" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -13318,7 +13000,7 @@
         <v>1141</v>
       </c>
       <c r="E517" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -13335,7 +13017,7 @@
         <v>1142</v>
       </c>
       <c r="E518" t="s">
-        <v>1384</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -13352,7 +13034,7 @@
         <v>1143</v>
       </c>
       <c r="E519" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="520" spans="1:5">
@@ -13369,7 +13051,7 @@
         <v>1144</v>
       </c>
       <c r="E520" t="s">
-        <v>1384</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="521" spans="1:5">
@@ -13386,7 +13068,7 @@
         <v>1145</v>
       </c>
       <c r="E521" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="522" spans="1:5">
@@ -13403,7 +13085,7 @@
         <v>1146</v>
       </c>
       <c r="E522" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="523" spans="1:5">
@@ -13420,7 +13102,7 @@
         <v>1147</v>
       </c>
       <c r="E523" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="524" spans="1:5">
@@ -13437,7 +13119,7 @@
         <v>1148</v>
       </c>
       <c r="E524" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="525" spans="1:5">
@@ -13454,7 +13136,7 @@
         <v>1149</v>
       </c>
       <c r="E525" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="526" spans="1:5">
@@ -13471,7 +13153,7 @@
         <v>1150</v>
       </c>
       <c r="E526" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="527" spans="1:5">
@@ -13488,7 +13170,7 @@
         <v>1151</v>
       </c>
       <c r="E527" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="528" spans="1:5">
@@ -13505,7 +13187,7 @@
         <v>1152</v>
       </c>
       <c r="E528" t="s">
-        <v>1384</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="529" spans="1:5">
@@ -13522,7 +13204,7 @@
         <v>1153</v>
       </c>
       <c r="E529" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -13539,7 +13221,7 @@
         <v>1154</v>
       </c>
       <c r="E530" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="531" spans="1:5">
@@ -13556,7 +13238,7 @@
         <v>1155</v>
       </c>
       <c r="E531" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="532" spans="1:5">
@@ -13573,7 +13255,7 @@
         <v>1156</v>
       </c>
       <c r="E532" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="533" spans="1:5">
@@ -13590,7 +13272,7 @@
         <v>1157</v>
       </c>
       <c r="E533" t="s">
-        <v>1384</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -13607,7 +13289,7 @@
         <v>1158</v>
       </c>
       <c r="E534" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -13624,7 +13306,7 @@
         <v>1159</v>
       </c>
       <c r="E535" t="s">
-        <v>1384</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="536" spans="1:5">
@@ -13641,7 +13323,7 @@
         <v>1160</v>
       </c>
       <c r="E536" t="s">
-        <v>1384</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="537" spans="1:5">
@@ -13658,7 +13340,7 @@
         <v>1161</v>
       </c>
       <c r="E537" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="538" spans="1:5">
@@ -13675,7 +13357,7 @@
         <v>1162</v>
       </c>
       <c r="E538" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="539" spans="1:5">
@@ -13692,7 +13374,7 @@
         <v>1163</v>
       </c>
       <c r="E539" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="540" spans="1:5">
@@ -13709,7 +13391,7 @@
         <v>1164</v>
       </c>
       <c r="E540" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -13726,7 +13408,7 @@
         <v>1165</v>
       </c>
       <c r="E541" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="542" spans="1:5">
@@ -13743,7 +13425,7 @@
         <v>1166</v>
       </c>
       <c r="E542" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -13760,7 +13442,7 @@
         <v>1167</v>
       </c>
       <c r="E543" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -13777,7 +13459,7 @@
         <v>1168</v>
       </c>
       <c r="E544" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="545" spans="1:5">
@@ -13794,7 +13476,7 @@
         <v>1169</v>
       </c>
       <c r="E545" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -13811,7 +13493,7 @@
         <v>1170</v>
       </c>
       <c r="E546" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="547" spans="1:5">
@@ -13828,7 +13510,7 @@
         <v>1171</v>
       </c>
       <c r="E547" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -13845,7 +13527,7 @@
         <v>1172</v>
       </c>
       <c r="E548" t="s">
-        <v>1384</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="549" spans="1:5">
@@ -13862,7 +13544,7 @@
         <v>1173</v>
       </c>
       <c r="E549" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -13879,7 +13561,7 @@
         <v>1174</v>
       </c>
       <c r="E550" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -13896,7 +13578,7 @@
         <v>1175</v>
       </c>
       <c r="E551" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="552" spans="1:5">
@@ -13913,7 +13595,7 @@
         <v>1176</v>
       </c>
       <c r="E552" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="553" spans="1:5">
@@ -13930,7 +13612,7 @@
         <v>1177</v>
       </c>
       <c r="E553" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -13947,7 +13629,7 @@
         <v>1178</v>
       </c>
       <c r="E554" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -13964,7 +13646,7 @@
         <v>1179</v>
       </c>
       <c r="E555" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="556" spans="1:5">
@@ -13981,7 +13663,7 @@
         <v>1180</v>
       </c>
       <c r="E556" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -13998,7 +13680,7 @@
         <v>1181</v>
       </c>
       <c r="E557" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -14015,7 +13697,7 @@
         <v>1182</v>
       </c>
       <c r="E558" t="s">
-        <v>1384</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -14032,7 +13714,7 @@
         <v>728</v>
       </c>
       <c r="E559" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -14049,7 +13731,7 @@
         <v>1183</v>
       </c>
       <c r="E560" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -14066,7 +13748,7 @@
         <v>1184</v>
       </c>
       <c r="E561" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="562" spans="1:5">
@@ -14083,7 +13765,7 @@
         <v>1185</v>
       </c>
       <c r="E562" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -14100,7 +13782,7 @@
         <v>1186</v>
       </c>
       <c r="E563" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -14117,7 +13799,7 @@
         <v>1187</v>
       </c>
       <c r="E564" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -14134,7 +13816,7 @@
         <v>1188</v>
       </c>
       <c r="E565" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -14151,7 +13833,7 @@
         <v>1189</v>
       </c>
       <c r="E566" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -14168,7 +13850,7 @@
         <v>1190</v>
       </c>
       <c r="E567" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -14185,7 +13867,7 @@
         <v>1191</v>
       </c>
       <c r="E568" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -14202,7 +13884,7 @@
         <v>1192</v>
       </c>
       <c r="E569" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -14219,7 +13901,7 @@
         <v>1193</v>
       </c>
       <c r="E570" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -14236,7 +13918,7 @@
         <v>1194</v>
       </c>
       <c r="E571" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -14253,7 +13935,7 @@
         <v>1195</v>
       </c>
       <c r="E572" t="s">
-        <v>1384</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -14270,7 +13952,7 @@
         <v>1196</v>
       </c>
       <c r="E573" t="s">
-        <v>1384</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -14287,7 +13969,7 @@
         <v>1197</v>
       </c>
       <c r="E574" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="575" spans="1:5">
@@ -14304,7 +13986,7 @@
         <v>1198</v>
       </c>
       <c r="E575" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -14321,7 +14003,7 @@
         <v>1199</v>
       </c>
       <c r="E576" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -14338,7 +14020,7 @@
         <v>1200</v>
       </c>
       <c r="E577" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="578" spans="1:5">
@@ -14355,7 +14037,7 @@
         <v>1201</v>
       </c>
       <c r="E578" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -14372,7 +14054,7 @@
         <v>1202</v>
       </c>
       <c r="E579" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -14389,7 +14071,7 @@
         <v>1203</v>
       </c>
       <c r="E580" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -14406,7 +14088,7 @@
         <v>1204</v>
       </c>
       <c r="E581" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -14423,7 +14105,7 @@
         <v>1205</v>
       </c>
       <c r="E582" t="s">
-        <v>1384</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -14440,7 +14122,7 @@
         <v>1206</v>
       </c>
       <c r="E583" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -14457,7 +14139,7 @@
         <v>1207</v>
       </c>
       <c r="E584" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -14474,7 +14156,7 @@
         <v>1208</v>
       </c>
       <c r="E585" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -14491,7 +14173,7 @@
         <v>1209</v>
       </c>
       <c r="E586" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -14508,7 +14190,7 @@
         <v>1210</v>
       </c>
       <c r="E587" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -14525,7 +14207,7 @@
         <v>1211</v>
       </c>
       <c r="E588" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -14542,7 +14224,7 @@
         <v>1212</v>
       </c>
       <c r="E589" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -14559,7 +14241,7 @@
         <v>1213</v>
       </c>
       <c r="E590" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -14576,7 +14258,7 @@
         <v>1214</v>
       </c>
       <c r="E591" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -14593,7 +14275,7 @@
         <v>1215</v>
       </c>
       <c r="E592" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -14610,7 +14292,7 @@
         <v>1216</v>
       </c>
       <c r="E593" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -14627,7 +14309,7 @@
         <v>1217</v>
       </c>
       <c r="E594" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -14644,7 +14326,7 @@
         <v>1218</v>
       </c>
       <c r="E595" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -14661,7 +14343,7 @@
         <v>1219</v>
       </c>
       <c r="E596" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -14678,7 +14360,7 @@
         <v>1220</v>
       </c>
       <c r="E597" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="598" spans="1:5">
@@ -14695,7 +14377,7 @@
         <v>1221</v>
       </c>
       <c r="E598" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="599" spans="1:5">
@@ -14712,7 +14394,7 @@
         <v>1222</v>
       </c>
       <c r="E599" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -14729,7 +14411,7 @@
         <v>1223</v>
       </c>
       <c r="E600" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -14746,7 +14428,7 @@
         <v>1224</v>
       </c>
       <c r="E601" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -14763,7 +14445,7 @@
         <v>1225</v>
       </c>
       <c r="E602" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="603" spans="1:5">
@@ -14780,7 +14462,7 @@
         <v>1226</v>
       </c>
       <c r="E603" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -14797,7 +14479,7 @@
         <v>1227</v>
       </c>
       <c r="E604" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -14814,7 +14496,7 @@
         <v>1228</v>
       </c>
       <c r="E605" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -14831,7 +14513,7 @@
         <v>1229</v>
       </c>
       <c r="E606" t="s">
-        <v>1384</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -14848,7 +14530,7 @@
         <v>1230</v>
       </c>
       <c r="E607" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -14865,7 +14547,7 @@
         <v>1231</v>
       </c>
       <c r="E608" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -14882,7 +14564,7 @@
         <v>1232</v>
       </c>
       <c r="E609" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -14899,7 +14581,7 @@
         <v>1233</v>
       </c>
       <c r="E610" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -14916,7 +14598,7 @@
         <v>1234</v>
       </c>
       <c r="E611" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -14933,7 +14615,7 @@
         <v>1235</v>
       </c>
       <c r="E612" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -14950,7 +14632,7 @@
         <v>1236</v>
       </c>
       <c r="E613" t="s">
-        <v>1384</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -14967,7 +14649,7 @@
         <v>1237</v>
       </c>
       <c r="E614" t="s">
-        <v>1384</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -14984,7 +14666,7 @@
         <v>1238</v>
       </c>
       <c r="E615" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -15001,7 +14683,7 @@
         <v>1239</v>
       </c>
       <c r="E616" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -15018,7 +14700,7 @@
         <v>1240</v>
       </c>
       <c r="E617" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -15035,7 +14717,7 @@
         <v>1241</v>
       </c>
       <c r="E618" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -15052,7 +14734,7 @@
         <v>1242</v>
       </c>
       <c r="E619" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -15069,7 +14751,7 @@
         <v>1243</v>
       </c>
       <c r="E620" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -15086,7 +14768,7 @@
         <v>1244</v>
       </c>
       <c r="E621" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -15103,7 +14785,7 @@
         <v>1245</v>
       </c>
       <c r="E622" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -15120,7 +14802,7 @@
         <v>1246</v>
       </c>
       <c r="E623" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -15137,7 +14819,7 @@
         <v>1247</v>
       </c>
       <c r="E624" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -15154,7 +14836,7 @@
         <v>1248</v>
       </c>
       <c r="E625" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -15171,7 +14853,7 @@
         <v>1249</v>
       </c>
       <c r="E626" t="s">
-        <v>1385</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -15188,7 +14870,7 @@
         <v>1250</v>
       </c>
       <c r="E627" t="s">
-        <v>1385</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -15205,7 +14887,7 @@
         <v>1251</v>
       </c>
       <c r="E628" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -15222,7 +14904,7 @@
         <v>1252</v>
       </c>
       <c r="E629" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -15239,7 +14921,7 @@
         <v>1253</v>
       </c>
       <c r="E630" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -15256,7 +14938,7 @@
         <v>1254</v>
       </c>
       <c r="E631" t="s">
-        <v>1385</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived_outputs/post_rescued_nrc_630_codebook.xlsx
+++ b/data/derived_outputs/post_rescued_nrc_630_codebook.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="1433">
   <si>
     <t>word</t>
   </si>
@@ -34,7 +34,7 @@
     <t>nrc_emotion</t>
   </si>
   <si>
-    <t>category_taxonomy</t>
+    <t>class_taxonomy</t>
   </si>
   <si>
     <t>vader_score</t>
@@ -3790,439 +3790,529 @@
     <t>刺激快感</t>
   </si>
   <si>
-    <t>Positive (V &gt; 0)</t>
-  </si>
-  <si>
-    <t>Zero / Neutral (V = 0)</t>
-  </si>
-  <si>
-    <t>Negative (V &lt; 0)</t>
-  </si>
-  <si>
-    <t>Positive/Negative Polarity Only</t>
+    <t>Positive (正向)</t>
+  </si>
+  <si>
+    <t>Zero / Neutral (中性)</t>
+  </si>
+  <si>
+    <t>Negative (负向)</t>
+  </si>
+  <si>
+    <t>Joy / Positive</t>
   </si>
   <si>
     <t>Joy</t>
   </si>
   <si>
+    <t>Anticipation, Joy, Trust</t>
+  </si>
+  <si>
+    <t>Joy, Surprise, Trust</t>
+  </si>
+  <si>
+    <t>Anticipation, Joy, Surprise, Trust</t>
+  </si>
+  <si>
+    <t>Joy, Trust</t>
+  </si>
+  <si>
+    <t>Anticipation, Joy</t>
+  </si>
+  <si>
+    <t>CATE (Low-Altitude Air Tourism Domain Discovery)</t>
+  </si>
+  <si>
+    <t>Joy, Surprise</t>
+  </si>
+  <si>
+    <t>Anticipation, Fear</t>
+  </si>
+  <si>
+    <t>Anger, Disgust, Sadness</t>
+  </si>
+  <si>
     <t>Surprise</t>
   </si>
   <si>
-    <t>CATE (Low-Altitude Domain Lexicon)</t>
+    <t>Anger, Disgust, Fear, Sadness</t>
+  </si>
+  <si>
+    <t>Anticipation, Joy, Surprise</t>
+  </si>
+  <si>
+    <t>Sadness</t>
+  </si>
+  <si>
+    <t>Disgust, Sadness</t>
+  </si>
+  <si>
+    <t>Anticipation, Joy, Sadness, Surprise, Trust</t>
+  </si>
+  <si>
+    <t>Anticipation, Trust</t>
+  </si>
+  <si>
+    <t>Fear, Joy, Surprise</t>
+  </si>
+  <si>
+    <t>Anticipation</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Fear, Sadness</t>
   </si>
   <si>
     <t>Fear</t>
   </si>
   <si>
-    <t>Sadness</t>
-  </si>
-  <si>
-    <t>Trust</t>
-  </si>
-  <si>
-    <t>Anticipation</t>
+    <t>Anticipation, Fear, Joy, Surprise</t>
+  </si>
+  <si>
+    <t>Anger, Fear</t>
+  </si>
+  <si>
+    <t>Fear, Joy, Trust</t>
+  </si>
+  <si>
+    <t>Anticipation, Fear, Sadness</t>
+  </si>
+  <si>
+    <t>Anger, Disgust, Fear, Joy, Sadness, Trust</t>
   </si>
   <si>
     <t>Anger</t>
   </si>
   <si>
+    <t>Surprise, Trust</t>
+  </si>
+  <si>
+    <t>Anticipation, Surprise</t>
+  </si>
+  <si>
+    <t>Anger, Anticipation, Fear, Sadness</t>
+  </si>
+  <si>
+    <t>Anger, Disgust, Fear, Sadness, Surprise</t>
+  </si>
+  <si>
+    <t>NRC Polarity Only (Positive/Negative)</t>
+  </si>
+  <si>
+    <t>Anger, Sadness</t>
+  </si>
+  <si>
+    <t>Morphological Rescued</t>
+  </si>
+  <si>
+    <t>Anger, Disgust, Fear, Surprise</t>
+  </si>
+  <si>
+    <t>Disgust, Fear</t>
+  </si>
+  <si>
+    <t>Anticipation, Fear, Surprise</t>
+  </si>
+  <si>
+    <t>Fear, Surprise</t>
+  </si>
+  <si>
+    <t>Anger, Anticipation, Fear, Joy, Surprise</t>
+  </si>
+  <si>
+    <t>Anger, Disgust</t>
+  </si>
+  <si>
+    <t>Anger, Anticipation, Disgust, Fear, Joy, Trust</t>
+  </si>
+  <si>
     <t>Disgust</t>
   </si>
   <si>
-    <t>CATE (Colloquial Superlative)</t>
-  </si>
-  <si>
-    <t>1a. Directly Mapped 8-Emotions</t>
-  </si>
-  <si>
-    <t>1b. Directly Mapped Polarity Only</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (respectful -&gt; respectful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (immaculate -&gt; immaculate)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (annoying -&gt; annoying)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (fuss -&gt; fuss)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (awful -&gt; awful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (awed -&gt; awed)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (bubbly -&gt; bubbly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (praise -&gt; praise)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (trustworthy -&gt; trustworthy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (satisfaction -&gt; satisfaction)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (ruined -&gt; ruined)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (proud -&gt; proud)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (marvellous -&gt; marvellous)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (intrusive -&gt; intrusive)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (glowing -&gt; glowing)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (frustrating -&gt; frustrating)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (bothered -&gt; bothered)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (authentic -&gt; authentic)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (tricky -&gt; tricky)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (worldly -&gt; worldly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (vibrant -&gt; vibrant)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (uneasy -&gt; uneasy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (precious -&gt; precious)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (safest -&gt; safest)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (responsible -&gt; responsible)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (pleasurable -&gt; pleasurable)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (apologetic -&gt; apologetic)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (bored -&gt; bored)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (soaking -&gt; soaking)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (stuffy -&gt; stuffy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (superbly -&gt; superbly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (wondrous -&gt; wondrous)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (satisfying -&gt; satisfying)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (wary -&gt; wary)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (trepidation -&gt; trepidation)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (surprising -&gt; surprising)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (superlative -&gt; superlative)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (sketchy -&gt; sketchy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (slick -&gt; slick)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (rewarding -&gt; rewarding)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (nervousness -&gt; nervousness)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (mad -&gt; mad)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (inviting -&gt; inviting)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (cheesy -&gt; cheesy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (admire -&gt; admire)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (mesmerized -&gt; mesmerized)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (unfortunate -&gt; unfortunate)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (stunningly -&gt; stunningly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (stunned -&gt; stunned)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (stability -&gt; stability)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (raving -&gt; raving)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (quaint -&gt; quaint)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (wonderfull -&gt; wonderful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (jealous -&gt; jealous)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (improving -&gt; improving)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (improvement -&gt; improvement)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (friendlier -&gt; friendlier)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (emotional -&gt; emotional)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (ecstatic -&gt; ecstatic)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (conscientious -&gt; conscientious)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (badly -&gt; badly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (unspoiled -&gt; unspoiled)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (terribly -&gt; terribly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (susceptible -&gt; susceptible)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (stuffed -&gt; stuffed)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (miserable -&gt; miserable)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (hassles -&gt; hassles)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (effortless -&gt; effortless)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (compliment -&gt; compliment)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (claustrophobia -&gt; claustrophobia)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (cheerfully -&gt; cheerfully)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (bummer -&gt; bummer)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (awkward -&gt; awkward)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (automatically -&gt; automatically)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (mindful -&gt; mindful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (yummy -&gt; yummy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (unstable -&gt; unstable)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (spoiled -&gt; spoiled)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (shocked -&gt; shocked)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (poorly -&gt; poorly)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (nerve -&gt; nerve)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (grace -&gt; grace)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (frustration -&gt; frustration)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (frightened -&gt; frightened)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (exhilaration -&gt; exhilaration)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (exhausted -&gt; exhausted)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (dissapointed -&gt; disappointed)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (cherished -&gt; cherish)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (annoyed -&gt; annoyed)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (strange -&gt; strange)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (reputable -&gt; reputable)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (ridiculous -&gt; ridiculous)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (rudely -&gt; rudely)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (serenity -&gt; serenity)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (relieved -&gt; relieved)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (suffered -&gt; suffered)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (unhappy -&gt; unhappy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (unpleasant -&gt; unpleasant)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (powerful -&gt; powerful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (worrying -&gt; worry)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (weird -&gt; weird)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (painful -&gt; painful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (panic -&gt; panic)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (laughter -&gt; laughter)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (hopeful -&gt; hopeful)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (hesitating -&gt; hesitating)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (gushing -&gt; gushing)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (exhilerating -&gt; exhilarating)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (enthusiastically -&gt; enthusiastically)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (curious -&gt; curious)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (confusion -&gt; confusion)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (classy -&gt; classy)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (captivated -&gt; captivated)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (alas -&gt; alas)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (reassurance -&gt; reassurance)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (inspirational -&gt; inspirational)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (jovial -&gt; jovial)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (precision -&gt; precision)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (gratitude -&gt; gratitude)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (relief -&gt; relief)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (sublime -&gt; sublime)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (timid -&gt; timid)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (warmest -&gt; warmest)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (hug -&gt; hug)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (amaze -&gt; amaze)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (frightening -&gt; frightening)</t>
-  </si>
-  <si>
-    <t>1c. Morphological Rescued (calmer -&gt; calmer)</t>
-  </si>
-  <si>
-    <t>2a. Class 2 Colloquial Superlatives</t>
-  </si>
-  <si>
-    <t>2b. Class 3 Domain Lexicon</t>
+    <t>Web 2.0 General Evaluative Term</t>
+  </si>
+  <si>
+    <t>1a. NRC 原生 8大情绪涵盖词 (286 Words)</t>
+  </si>
+  <si>
+    <t>2b. Class 3 低空观光领域专有采掘词 (17 Words)</t>
+  </si>
+  <si>
+    <t>1b. NRC 原生 仅极性涵盖词 (72 Words)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (respectful -&gt; respectful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (immaculate -&gt; immaculate)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (annoying -&gt; annoying)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (fuss -&gt; fuss)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (awful -&gt; awful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (bubbly -&gt; bubbly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (praise -&gt; praise)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (trustworthy -&gt; trustworthy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (satisfaction -&gt; satisfaction)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (ruined -&gt; ruined)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (proud -&gt; proud)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (marvellous -&gt; marvellous)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (intrusive -&gt; intrusive)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (glowing -&gt; glowing)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (frustrating -&gt; frustrating)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (bothered -&gt; bothered)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (authentic -&gt; authentic)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (tricky -&gt; tricky)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (worldly -&gt; worldly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (vibrant -&gt; vibrant)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (uneasy -&gt; uneasy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (precious -&gt; precious)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (safest -&gt; safest)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (responsible -&gt; responsible)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (pleasurable -&gt; pleasurable)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (apologetic -&gt; apologetic)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (bored -&gt; bored)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (soaking -&gt; soaking)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (stuffy -&gt; stuffy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (superbly -&gt; superbly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (wondrous -&gt; wondrous)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (satisfying -&gt; satisfying)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (wary -&gt; wary)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (trepidation -&gt; trepidation)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (surprising -&gt; surprising)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (superlative -&gt; superlative)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (sketchy -&gt; sketchy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (slick -&gt; slick)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (rewarding -&gt; rewarding)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (nervousness -&gt; nervousness)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (mad -&gt; mad)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (inviting -&gt; inviting)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (cheesy -&gt; cheesy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (admire -&gt; admire)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (mesmerized -&gt; mesmerized)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (unfortunate -&gt; unfortunate)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (stunned -&gt; stunned)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (stability -&gt; stability)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (raving -&gt; raving)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (quaint -&gt; quaint)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (wonderfull -&gt; wonderful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (jealous -&gt; jealous)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (improving -&gt; improving)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (improvement -&gt; improvement)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (friendlier -&gt; friendlier)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (emotional -&gt; emotional)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (ecstatic -&gt; ecstatic)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (conscientious -&gt; conscientious)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (badly -&gt; badly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (unspoiled -&gt; unspoiled)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (terribly -&gt; terribly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (susceptible -&gt; susceptible)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (stuffed -&gt; stuffed)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (miserable -&gt; miserable)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (hassles -&gt; hassles)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (effortless -&gt; effortless)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (compliment -&gt; compliment)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (cheerfully -&gt; cheerfully)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (bummer -&gt; bummer)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (awkward -&gt; awkward)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (automatically -&gt; automatically)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (mindful -&gt; mindful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (yummy -&gt; yummy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (unstable -&gt; unstable)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (spoiled -&gt; spoiled)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (shocked -&gt; shocked)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (poorly -&gt; poorly)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (nerve -&gt; nerve)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (grace -&gt; grace)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (frustration -&gt; frustration)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (frightened -&gt; frightened)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (exhilaration -&gt; exhilaration)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (exhausted -&gt; exhausted)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (dissapointed -&gt; disappointed)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (cherished -&gt; cherish)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (annoyed -&gt; annoyed)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (strange -&gt; strange)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (reputable -&gt; reputable)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (ridiculous -&gt; ridiculous)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (rudely -&gt; rudely)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (serenity -&gt; serenity)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (relieved -&gt; relieved)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (suffered -&gt; suffered)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (unhappy -&gt; unhappy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (unpleasant -&gt; unpleasant)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (powerful -&gt; powerful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (worrying -&gt; worry)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (weird -&gt; weird)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (painful -&gt; painful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (panic -&gt; panic)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (laughter -&gt; laughter)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (hopeful -&gt; hopeful)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (hesitating -&gt; hesitating)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (gushing -&gt; gushing)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (exhilerating -&gt; exhilarating)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (enthusiastically -&gt; enthusiastically)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (curious -&gt; curious)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (confusion -&gt; confusion)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (classy -&gt; classy)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (captivated -&gt; captivated)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (alas -&gt; alas)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (reassurance -&gt; reassurance)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (inspirational -&gt; inspirational)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (jovial -&gt; jovial)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (precision -&gt; precision)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (gratitude -&gt; gratitude)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (relief -&gt; relief)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (timid -&gt; timid)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (warmest -&gt; warmest)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (hug -&gt; hug)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (amaze -&gt; amaze)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (frightening -&gt; frightening)</t>
+  </si>
+  <si>
+    <t>1c. Class 1 语法变形拯救归纳词 (calmer -&gt; calmer)</t>
+  </si>
+  <si>
+    <t>2a. Class 2 Web 2.0 口语极致形容与评价词 (128 Words)</t>
   </si>
 </sst>
 </file>
@@ -4629,7 +4719,7 @@
         <v>1261</v>
       </c>
       <c r="G2" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H2">
         <v>3.1</v>
@@ -4655,7 +4745,7 @@
         <v>1261</v>
       </c>
       <c r="G3" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H3">
         <v>2.8</v>
@@ -4681,7 +4771,7 @@
         <v>1262</v>
       </c>
       <c r="G4" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H4">
         <v>2.9</v>
@@ -4707,7 +4797,7 @@
         <v>1261</v>
       </c>
       <c r="G5" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H5">
         <v>3.2</v>
@@ -4730,10 +4820,10 @@
         <v>1258</v>
       </c>
       <c r="F6" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G6" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H6">
         <v>2.2</v>
@@ -4759,7 +4849,7 @@
         <v>1261</v>
       </c>
       <c r="G7" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H7">
         <v>0.9</v>
@@ -4782,10 +4872,10 @@
         <v>1258</v>
       </c>
       <c r="F8" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="G8" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H8">
         <v>2.7</v>
@@ -4808,10 +4898,10 @@
         <v>1258</v>
       </c>
       <c r="F9" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G9" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H9">
         <v>1.9</v>
@@ -4837,7 +4927,7 @@
         <v>1261</v>
       </c>
       <c r="G10" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H10">
         <v>3.1</v>
@@ -4860,10 +4950,10 @@
         <v>1258</v>
       </c>
       <c r="F11" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G11" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H11">
         <v>2.7</v>
@@ -4889,7 +4979,7 @@
         <v>1261</v>
       </c>
       <c r="G12" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H12">
         <v>2.6</v>
@@ -4915,7 +5005,7 @@
         <v>1261</v>
       </c>
       <c r="G13" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H13">
         <v>1.8</v>
@@ -4938,10 +5028,10 @@
         <v>1258</v>
       </c>
       <c r="F14" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="G14" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H14">
         <v>2.3</v>
@@ -4964,10 +5054,10 @@
         <v>1259</v>
       </c>
       <c r="F15" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="G15" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -4990,10 +5080,10 @@
         <v>1259</v>
       </c>
       <c r="F16" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="G16" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5019,7 +5109,7 @@
         <v>1261</v>
       </c>
       <c r="G17" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H17">
         <v>1.9</v>
@@ -5042,10 +5132,10 @@
         <v>1258</v>
       </c>
       <c r="F18" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G18" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H18">
         <v>2.7</v>
@@ -5071,7 +5161,7 @@
         <v>1261</v>
       </c>
       <c r="G19" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H19">
         <v>2.9</v>
@@ -5097,7 +5187,7 @@
         <v>1261</v>
       </c>
       <c r="G20" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H20">
         <v>2.3</v>
@@ -5120,10 +5210,10 @@
         <v>1258</v>
       </c>
       <c r="F21" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G21" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -5146,10 +5236,10 @@
         <v>1258</v>
       </c>
       <c r="F22" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G22" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H22">
         <v>1.8</v>
@@ -5172,10 +5262,10 @@
         <v>1258</v>
       </c>
       <c r="F23" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="G23" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -5201,7 +5291,7 @@
         <v>1261</v>
       </c>
       <c r="G24" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H24">
         <v>1.7</v>
@@ -5227,7 +5317,7 @@
         <v>1261</v>
       </c>
       <c r="G25" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H25">
         <v>1.3</v>
@@ -5253,7 +5343,7 @@
         <v>1262</v>
       </c>
       <c r="G26" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H26">
         <v>1.7</v>
@@ -5276,10 +5366,10 @@
         <v>1258</v>
       </c>
       <c r="F27" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="G27" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H27">
         <v>1.8</v>
@@ -5302,10 +5392,10 @@
         <v>1258</v>
       </c>
       <c r="F28" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G28" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H28">
         <v>2.4</v>
@@ -5328,10 +5418,10 @@
         <v>1259</v>
       </c>
       <c r="F29" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="G29" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -5354,10 +5444,10 @@
         <v>1258</v>
       </c>
       <c r="F30" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G30" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H30">
         <v>2.7</v>
@@ -5380,10 +5470,10 @@
         <v>1258</v>
       </c>
       <c r="F31" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G31" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H31">
         <v>1.6</v>
@@ -5406,10 +5496,10 @@
         <v>1260</v>
       </c>
       <c r="F32" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="G32" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H32">
         <v>-1.1</v>
@@ -5435,7 +5525,7 @@
         <v>1261</v>
       </c>
       <c r="G33" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H33">
         <v>2.4</v>
@@ -5458,10 +5548,10 @@
         <v>1260</v>
       </c>
       <c r="F34" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G34" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H34">
         <v>-2.1</v>
@@ -5487,7 +5577,7 @@
         <v>1262</v>
       </c>
       <c r="G35" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H35">
         <v>3</v>
@@ -5513,7 +5603,7 @@
         <v>1261</v>
       </c>
       <c r="G36" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H36">
         <v>1.9</v>
@@ -5539,7 +5629,7 @@
         <v>1261</v>
       </c>
       <c r="G37" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -5565,7 +5655,7 @@
         <v>1262</v>
       </c>
       <c r="G38" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H38">
         <v>3.2</v>
@@ -5588,10 +5678,10 @@
         <v>1259</v>
       </c>
       <c r="F39" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="G39" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -5617,7 +5707,7 @@
         <v>1262</v>
       </c>
       <c r="G40" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -5640,10 +5730,10 @@
         <v>1259</v>
       </c>
       <c r="F41" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G41" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -5666,10 +5756,10 @@
         <v>1260</v>
       </c>
       <c r="F42" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G42" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H42">
         <v>-2.5</v>
@@ -5692,10 +5782,10 @@
         <v>1258</v>
       </c>
       <c r="F43" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G43" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H43">
         <v>2.2</v>
@@ -5721,7 +5811,7 @@
         <v>1261</v>
       </c>
       <c r="G44" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -5744,10 +5834,10 @@
         <v>1258</v>
       </c>
       <c r="F45" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G45" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H45">
         <v>2.3</v>
@@ -5770,10 +5860,10 @@
         <v>1259</v>
       </c>
       <c r="F46" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G46" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -5799,7 +5889,7 @@
         <v>1261</v>
       </c>
       <c r="G47" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H47">
         <v>0.8</v>
@@ -5825,7 +5915,7 @@
         <v>1261</v>
       </c>
       <c r="G48" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H48">
         <v>1.9</v>
@@ -5851,7 +5941,7 @@
         <v>1261</v>
       </c>
       <c r="G49" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -5877,7 +5967,7 @@
         <v>1261</v>
       </c>
       <c r="G50" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H50">
         <v>-0.4</v>
@@ -5900,10 +5990,10 @@
         <v>1260</v>
       </c>
       <c r="F51" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G51" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H51">
         <v>-1.8</v>
@@ -5926,10 +6016,10 @@
         <v>1258</v>
       </c>
       <c r="F52" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G52" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H52">
         <v>2.9</v>
@@ -5952,10 +6042,10 @@
         <v>1259</v>
       </c>
       <c r="F53" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="G53" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -5978,10 +6068,10 @@
         <v>1260</v>
       </c>
       <c r="F54" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G54" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H54">
         <v>-2.3</v>
@@ -6004,10 +6094,10 @@
         <v>1258</v>
       </c>
       <c r="F55" t="s">
-        <v>1262</v>
+        <v>1277</v>
       </c>
       <c r="G55" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H55">
         <v>2.8</v>
@@ -6030,10 +6120,10 @@
         <v>1258</v>
       </c>
       <c r="F56" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G56" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H56">
         <v>2.1</v>
@@ -6059,7 +6149,7 @@
         <v>1261</v>
       </c>
       <c r="G57" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H57">
         <v>1.3</v>
@@ -6085,7 +6175,7 @@
         <v>1261</v>
       </c>
       <c r="G58" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H58">
         <v>2.1</v>
@@ -6111,7 +6201,7 @@
         <v>1261</v>
       </c>
       <c r="G59" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H59">
         <v>-1.4</v>
@@ -6137,7 +6227,7 @@
         <v>1261</v>
       </c>
       <c r="G60" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H60">
         <v>1.9</v>
@@ -6160,10 +6250,10 @@
         <v>1258</v>
       </c>
       <c r="F61" t="s">
-        <v>1267</v>
+        <v>1278</v>
       </c>
       <c r="G61" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H61">
         <v>1.8</v>
@@ -6189,7 +6279,7 @@
         <v>1261</v>
       </c>
       <c r="G62" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H62">
         <v>2</v>
@@ -6212,10 +6302,10 @@
         <v>1258</v>
       </c>
       <c r="F63" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="G63" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H63">
         <v>1.9</v>
@@ -6241,7 +6331,7 @@
         <v>1261</v>
       </c>
       <c r="G64" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H64">
         <v>1.8</v>
@@ -6267,7 +6357,7 @@
         <v>1261</v>
       </c>
       <c r="G65" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -6290,10 +6380,10 @@
         <v>1259</v>
       </c>
       <c r="F66" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="G66" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -6319,7 +6409,7 @@
         <v>1261</v>
       </c>
       <c r="G67" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H67">
         <v>3.1</v>
@@ -6342,10 +6432,10 @@
         <v>1258</v>
       </c>
       <c r="F68" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="G68" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H68">
         <v>0.9</v>
@@ -6368,10 +6458,10 @@
         <v>1258</v>
       </c>
       <c r="F69" t="s">
-        <v>1262</v>
+        <v>1279</v>
       </c>
       <c r="G69" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H69">
         <v>1.1</v>
@@ -6397,7 +6487,7 @@
         <v>1261</v>
       </c>
       <c r="G70" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H70">
         <v>0.8</v>
@@ -6420,10 +6510,10 @@
         <v>1258</v>
       </c>
       <c r="F71" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G71" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H71">
         <v>2.8</v>
@@ -6449,7 +6539,7 @@
         <v>1261</v>
       </c>
       <c r="G72" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -6472,10 +6562,10 @@
         <v>1259</v>
       </c>
       <c r="F73" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="G73" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -6498,10 +6588,10 @@
         <v>1258</v>
       </c>
       <c r="F74" t="s">
-        <v>1268</v>
+        <v>1280</v>
       </c>
       <c r="G74" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H74">
         <v>1.5</v>
@@ -6524,10 +6614,10 @@
         <v>1258</v>
       </c>
       <c r="F75" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G75" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H75">
         <v>1.4</v>
@@ -6550,10 +6640,10 @@
         <v>1259</v>
       </c>
       <c r="F76" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="G76" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -6576,10 +6666,10 @@
         <v>1258</v>
       </c>
       <c r="F77" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G77" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H77">
         <v>1.3</v>
@@ -6602,10 +6692,10 @@
         <v>1259</v>
       </c>
       <c r="F78" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G78" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -6631,7 +6721,7 @@
         <v>1261</v>
       </c>
       <c r="G79" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H79">
         <v>2.2</v>
@@ -6654,10 +6744,10 @@
         <v>1258</v>
       </c>
       <c r="F80" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G80" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H80">
         <v>1.9</v>
@@ -6683,7 +6773,7 @@
         <v>1261</v>
       </c>
       <c r="G81" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H81">
         <v>3.2</v>
@@ -6706,10 +6796,10 @@
         <v>1259</v>
       </c>
       <c r="F82" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="G82" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -6732,10 +6822,10 @@
         <v>1258</v>
       </c>
       <c r="F83" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G83" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H83">
         <v>1.7</v>
@@ -6761,7 +6851,7 @@
         <v>1261</v>
       </c>
       <c r="G84" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H84">
         <v>2.7</v>
@@ -6784,10 +6874,10 @@
         <v>1259</v>
       </c>
       <c r="F85" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G85" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -6810,10 +6900,10 @@
         <v>1259</v>
       </c>
       <c r="F86" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G86" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -6836,10 +6926,10 @@
         <v>1260</v>
       </c>
       <c r="F87" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G87" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H87">
         <v>-1.2</v>
@@ -6862,10 +6952,10 @@
         <v>1260</v>
       </c>
       <c r="F88" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="G88" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H88">
         <v>-1.9</v>
@@ -6891,7 +6981,7 @@
         <v>1261</v>
       </c>
       <c r="G89" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -6914,10 +7004,10 @@
         <v>1259</v>
       </c>
       <c r="F90" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G90" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -6943,7 +7033,7 @@
         <v>1261</v>
       </c>
       <c r="G91" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H91">
         <v>-2.1</v>
@@ -6969,7 +7059,7 @@
         <v>1261</v>
       </c>
       <c r="G92" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -6995,7 +7085,7 @@
         <v>1262</v>
       </c>
       <c r="G93" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H93">
         <v>2.9</v>
@@ -7021,7 +7111,7 @@
         <v>1262</v>
       </c>
       <c r="G94" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H94">
         <v>1.9</v>
@@ -7047,7 +7137,7 @@
         <v>1261</v>
       </c>
       <c r="G95" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H95">
         <v>2.2</v>
@@ -7073,7 +7163,7 @@
         <v>1261</v>
       </c>
       <c r="G96" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -7099,7 +7189,7 @@
         <v>1261</v>
       </c>
       <c r="G97" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H97">
         <v>2.3</v>
@@ -7122,10 +7212,10 @@
         <v>1258</v>
       </c>
       <c r="F98" t="s">
-        <v>1262</v>
+        <v>1284</v>
       </c>
       <c r="G98" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H98">
         <v>1.5</v>
@@ -7148,10 +7238,10 @@
         <v>1258</v>
       </c>
       <c r="F99" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G99" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H99">
         <v>2.1</v>
@@ -7177,7 +7267,7 @@
         <v>1261</v>
       </c>
       <c r="G100" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H100">
         <v>1.1</v>
@@ -7203,7 +7293,7 @@
         <v>1261</v>
       </c>
       <c r="G101" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -7229,7 +7319,7 @@
         <v>1261</v>
       </c>
       <c r="G102" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H102">
         <v>-0.3</v>
@@ -7255,7 +7345,7 @@
         <v>1261</v>
       </c>
       <c r="G103" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H103">
         <v>2.2</v>
@@ -7278,10 +7368,10 @@
         <v>1258</v>
       </c>
       <c r="F104" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G104" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H104">
         <v>1.5</v>
@@ -7304,10 +7394,10 @@
         <v>1260</v>
       </c>
       <c r="F105" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G105" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H105">
         <v>-1.7</v>
@@ -7333,7 +7423,7 @@
         <v>1261</v>
       </c>
       <c r="G106" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -7359,7 +7449,7 @@
         <v>1261</v>
       </c>
       <c r="G107" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H107">
         <v>2.2</v>
@@ -7382,10 +7472,10 @@
         <v>1260</v>
       </c>
       <c r="F108" t="s">
-        <v>1265</v>
+        <v>1285</v>
       </c>
       <c r="G108" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H108">
         <v>-2.2</v>
@@ -7408,10 +7498,10 @@
         <v>1259</v>
       </c>
       <c r="F109" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G109" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -7437,7 +7527,7 @@
         <v>1261</v>
       </c>
       <c r="G110" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H110">
         <v>1.9</v>
@@ -7460,10 +7550,10 @@
         <v>1258</v>
       </c>
       <c r="F111" t="s">
-        <v>1262</v>
+        <v>1286</v>
       </c>
       <c r="G111" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H111">
         <v>2.3</v>
@@ -7486,10 +7576,10 @@
         <v>1260</v>
       </c>
       <c r="F112" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G112" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H112">
         <v>-1.5</v>
@@ -7512,10 +7602,10 @@
         <v>1259</v>
       </c>
       <c r="F113" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G113" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -7541,7 +7631,7 @@
         <v>1261</v>
       </c>
       <c r="G114" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H114">
         <v>2</v>
@@ -7564,10 +7654,10 @@
         <v>1258</v>
       </c>
       <c r="F115" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G115" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H115">
         <v>2.2</v>
@@ -7593,7 +7683,7 @@
         <v>1261</v>
       </c>
       <c r="G116" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -7616,10 +7706,10 @@
         <v>1260</v>
       </c>
       <c r="F117" t="s">
-        <v>1265</v>
+        <v>1287</v>
       </c>
       <c r="G117" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H117">
         <v>-1.9</v>
@@ -7645,7 +7735,7 @@
         <v>1261</v>
       </c>
       <c r="G118" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -7671,7 +7761,7 @@
         <v>1261</v>
       </c>
       <c r="G119" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H119">
         <v>2.6</v>
@@ -7694,10 +7784,10 @@
         <v>1259</v>
       </c>
       <c r="F120" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G120" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -7723,7 +7813,7 @@
         <v>1261</v>
       </c>
       <c r="G121" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H121">
         <v>1.7</v>
@@ -7746,10 +7836,10 @@
         <v>1258</v>
       </c>
       <c r="F122" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G122" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H122">
         <v>2</v>
@@ -7775,7 +7865,7 @@
         <v>1261</v>
       </c>
       <c r="G123" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -7801,7 +7891,7 @@
         <v>1261</v>
       </c>
       <c r="G124" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H124">
         <v>2.3</v>
@@ -7827,7 +7917,7 @@
         <v>1261</v>
       </c>
       <c r="G125" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H125">
         <v>-2.1</v>
@@ -7853,7 +7943,7 @@
         <v>1261</v>
       </c>
       <c r="G126" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H126">
         <v>-2.2</v>
@@ -7879,7 +7969,7 @@
         <v>1261</v>
       </c>
       <c r="G127" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H127">
         <v>2.2</v>
@@ -7902,10 +7992,10 @@
         <v>1259</v>
       </c>
       <c r="F128" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="G128" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -7931,7 +8021,7 @@
         <v>1261</v>
       </c>
       <c r="G129" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H129">
         <v>1.7</v>
@@ -7954,10 +8044,10 @@
         <v>1258</v>
       </c>
       <c r="F130" t="s">
-        <v>1262</v>
+        <v>1288</v>
       </c>
       <c r="G130" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H130">
         <v>2.3</v>
@@ -7983,7 +8073,7 @@
         <v>1261</v>
       </c>
       <c r="G131" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -8006,10 +8096,10 @@
         <v>1258</v>
       </c>
       <c r="F132" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="G132" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H132">
         <v>1.9</v>
@@ -8035,7 +8125,7 @@
         <v>1261</v>
       </c>
       <c r="G133" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -8061,7 +8151,7 @@
         <v>1261</v>
       </c>
       <c r="G134" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H134">
         <v>1.6</v>
@@ -8087,7 +8177,7 @@
         <v>1261</v>
       </c>
       <c r="G135" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -8113,7 +8203,7 @@
         <v>1261</v>
       </c>
       <c r="G136" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -8139,7 +8229,7 @@
         <v>1261</v>
       </c>
       <c r="G137" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -8165,7 +8255,7 @@
         <v>1261</v>
       </c>
       <c r="G138" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H138">
         <v>2.5</v>
@@ -8191,7 +8281,7 @@
         <v>1261</v>
       </c>
       <c r="G139" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H139">
         <v>2</v>
@@ -8214,10 +8304,10 @@
         <v>1258</v>
       </c>
       <c r="F140" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G140" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H140">
         <v>2.8</v>
@@ -8243,7 +8333,7 @@
         <v>1261</v>
       </c>
       <c r="G141" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -8266,10 +8356,10 @@
         <v>1258</v>
       </c>
       <c r="F142" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G142" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H142">
         <v>1.5</v>
@@ -8295,7 +8385,7 @@
         <v>1261</v>
       </c>
       <c r="G143" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -8321,7 +8411,7 @@
         <v>1262</v>
       </c>
       <c r="G144" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H144">
         <v>1.4</v>
@@ -8347,7 +8437,7 @@
         <v>1261</v>
       </c>
       <c r="G145" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H145">
         <v>1.8</v>
@@ -8373,7 +8463,7 @@
         <v>1261</v>
       </c>
       <c r="G146" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H146">
         <v>2</v>
@@ -8399,7 +8489,7 @@
         <v>1261</v>
       </c>
       <c r="G147" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H147">
         <v>1.4</v>
@@ -8425,7 +8515,7 @@
         <v>1261</v>
       </c>
       <c r="G148" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -8448,10 +8538,10 @@
         <v>1258</v>
       </c>
       <c r="F149" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G149" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H149">
         <v>1.2</v>
@@ -8477,7 +8567,7 @@
         <v>1261</v>
       </c>
       <c r="G150" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -8503,7 +8593,7 @@
         <v>1261</v>
       </c>
       <c r="G151" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -8529,7 +8619,7 @@
         <v>1261</v>
       </c>
       <c r="G152" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H152">
         <v>3.2</v>
@@ -8555,7 +8645,7 @@
         <v>1261</v>
       </c>
       <c r="G153" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H153">
         <v>2.4</v>
@@ -8578,10 +8668,10 @@
         <v>1258</v>
       </c>
       <c r="F154" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G154" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H154">
         <v>2.2</v>
@@ -8604,10 +8694,10 @@
         <v>1259</v>
       </c>
       <c r="F155" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G155" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -8630,10 +8720,10 @@
         <v>1259</v>
       </c>
       <c r="F156" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G156" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -8659,7 +8749,7 @@
         <v>1261</v>
       </c>
       <c r="G157" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H157">
         <v>0</v>
@@ -8682,10 +8772,10 @@
         <v>1258</v>
       </c>
       <c r="F158" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G158" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H158">
         <v>2</v>
@@ -8711,7 +8801,7 @@
         <v>1261</v>
       </c>
       <c r="G159" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H159">
         <v>-1.8</v>
@@ -8737,7 +8827,7 @@
         <v>1261</v>
       </c>
       <c r="G160" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -8763,7 +8853,7 @@
         <v>1261</v>
       </c>
       <c r="G161" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -8789,7 +8879,7 @@
         <v>1261</v>
       </c>
       <c r="G162" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -8815,7 +8905,7 @@
         <v>1261</v>
       </c>
       <c r="G163" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -8841,7 +8931,7 @@
         <v>1261</v>
       </c>
       <c r="G164" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H164">
         <v>2.6</v>
@@ -8867,7 +8957,7 @@
         <v>1261</v>
       </c>
       <c r="G165" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -8890,10 +8980,10 @@
         <v>1258</v>
       </c>
       <c r="F166" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G166" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H166">
         <v>2.4</v>
@@ -8916,10 +9006,10 @@
         <v>1258</v>
       </c>
       <c r="F167" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G167" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H167">
         <v>1.9</v>
@@ -8945,7 +9035,7 @@
         <v>1262</v>
       </c>
       <c r="G168" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H168">
         <v>2.8</v>
@@ -8971,7 +9061,7 @@
         <v>1262</v>
       </c>
       <c r="G169" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H169">
         <v>1.7</v>
@@ -8997,7 +9087,7 @@
         <v>1261</v>
       </c>
       <c r="G170" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H170">
         <v>1.9</v>
@@ -9023,7 +9113,7 @@
         <v>1261</v>
       </c>
       <c r="G171" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -9046,10 +9136,10 @@
         <v>1258</v>
       </c>
       <c r="F172" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G172" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H172">
         <v>2.2</v>
@@ -9072,10 +9162,10 @@
         <v>1259</v>
       </c>
       <c r="F173" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G173" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -9101,7 +9191,7 @@
         <v>1261</v>
       </c>
       <c r="G174" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H174">
         <v>-0.4</v>
@@ -9127,7 +9217,7 @@
         <v>1261</v>
       </c>
       <c r="G175" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -9153,7 +9243,7 @@
         <v>1261</v>
       </c>
       <c r="G176" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H176">
         <v>2.3</v>
@@ -9179,7 +9269,7 @@
         <v>1261</v>
       </c>
       <c r="G177" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -9202,10 +9292,10 @@
         <v>1260</v>
       </c>
       <c r="F178" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G178" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H178">
         <v>-2.2</v>
@@ -9228,10 +9318,10 @@
         <v>1259</v>
       </c>
       <c r="F179" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G179" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -9254,10 +9344,10 @@
         <v>1260</v>
       </c>
       <c r="F180" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G180" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H180">
         <v>-2.7</v>
@@ -9283,7 +9373,7 @@
         <v>1262</v>
       </c>
       <c r="G181" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H181">
         <v>2.7</v>
@@ -9306,10 +9396,10 @@
         <v>1258</v>
       </c>
       <c r="F182" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G182" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H182">
         <v>1.6</v>
@@ -9335,7 +9425,7 @@
         <v>1261</v>
       </c>
       <c r="G183" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H183">
         <v>3.2</v>
@@ -9361,7 +9451,7 @@
         <v>1261</v>
       </c>
       <c r="G184" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H184">
         <v>-1.6</v>
@@ -9387,7 +9477,7 @@
         <v>1261</v>
       </c>
       <c r="G185" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H185">
         <v>1.3</v>
@@ -9410,10 +9500,10 @@
         <v>1260</v>
       </c>
       <c r="F186" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="G186" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H186">
         <v>-0.7</v>
@@ -9436,10 +9526,10 @@
         <v>1258</v>
       </c>
       <c r="F187" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="G187" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H187">
         <v>2.6</v>
@@ -9462,10 +9552,10 @@
         <v>1259</v>
       </c>
       <c r="F188" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G188" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -9488,10 +9578,10 @@
         <v>1258</v>
       </c>
       <c r="F189" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G189" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H189">
         <v>1.6</v>
@@ -9517,7 +9607,7 @@
         <v>1261</v>
       </c>
       <c r="G190" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H190">
         <v>2.2</v>
@@ -9540,10 +9630,10 @@
         <v>1258</v>
       </c>
       <c r="F191" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G191" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H191">
         <v>2.3</v>
@@ -9566,10 +9656,10 @@
         <v>1258</v>
       </c>
       <c r="F192" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G192" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H192">
         <v>1.9</v>
@@ -9595,7 +9685,7 @@
         <v>1261</v>
       </c>
       <c r="G193" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H193">
         <v>1.9</v>
@@ -9621,7 +9711,7 @@
         <v>1261</v>
       </c>
       <c r="G194" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H194">
         <v>2.3</v>
@@ -9647,7 +9737,7 @@
         <v>1261</v>
       </c>
       <c r="G195" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H195">
         <v>-1.7</v>
@@ -9670,10 +9760,10 @@
         <v>1260</v>
       </c>
       <c r="F196" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G196" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H196">
         <v>-2.3</v>
@@ -9699,7 +9789,7 @@
         <v>1261</v>
       </c>
       <c r="G197" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H197">
         <v>1.9</v>
@@ -9725,7 +9815,7 @@
         <v>1261</v>
       </c>
       <c r="G198" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H198">
         <v>1.8</v>
@@ -9751,7 +9841,7 @@
         <v>1261</v>
       </c>
       <c r="G199" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H199">
         <v>2.4</v>
@@ -9777,7 +9867,7 @@
         <v>1261</v>
       </c>
       <c r="G200" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H200">
         <v>0</v>
@@ -9803,7 +9893,7 @@
         <v>1261</v>
       </c>
       <c r="G201" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -9829,7 +9919,7 @@
         <v>1262</v>
       </c>
       <c r="G202" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H202">
         <v>1.8</v>
@@ -9852,10 +9942,10 @@
         <v>1258</v>
       </c>
       <c r="F203" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="G203" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H203">
         <v>2.9</v>
@@ -9881,7 +9971,7 @@
         <v>1261</v>
       </c>
       <c r="G204" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -9904,10 +9994,10 @@
         <v>1259</v>
       </c>
       <c r="F205" t="s">
-        <v>1267</v>
+        <v>1290</v>
       </c>
       <c r="G205" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H205">
         <v>0</v>
@@ -9930,10 +10020,10 @@
         <v>1260</v>
       </c>
       <c r="F206" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G206" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H206">
         <v>-2.1</v>
@@ -9959,7 +10049,7 @@
         <v>1261</v>
       </c>
       <c r="G207" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H207">
         <v>1.7</v>
@@ -9982,10 +10072,10 @@
         <v>1259</v>
       </c>
       <c r="F208" t="s">
-        <v>1262</v>
+        <v>1284</v>
       </c>
       <c r="G208" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H208">
         <v>0</v>
@@ -10011,7 +10101,7 @@
         <v>1261</v>
       </c>
       <c r="G209" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H209">
         <v>0</v>
@@ -10037,7 +10127,7 @@
         <v>1261</v>
       </c>
       <c r="G210" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H210">
         <v>1.8</v>
@@ -10063,7 +10153,7 @@
         <v>1261</v>
       </c>
       <c r="G211" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H211">
         <v>0</v>
@@ -10086,10 +10176,10 @@
         <v>1258</v>
       </c>
       <c r="F212" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G212" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H212">
         <v>2</v>
@@ -10115,7 +10205,7 @@
         <v>1261</v>
       </c>
       <c r="G213" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H213">
         <v>0</v>
@@ -10141,7 +10231,7 @@
         <v>1261</v>
       </c>
       <c r="G214" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H214">
         <v>1.9</v>
@@ -10164,10 +10254,10 @@
         <v>1260</v>
       </c>
       <c r="F215" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="G215" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H215">
         <v>-3</v>
@@ -10193,7 +10283,7 @@
         <v>1261</v>
       </c>
       <c r="G216" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H216">
         <v>1.5</v>
@@ -10219,7 +10309,7 @@
         <v>1262</v>
       </c>
       <c r="G217" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H217">
         <v>2.6</v>
@@ -10245,7 +10335,7 @@
         <v>1261</v>
       </c>
       <c r="G218" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -10271,7 +10361,7 @@
         <v>1261</v>
       </c>
       <c r="G219" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H219">
         <v>2.7</v>
@@ -10297,7 +10387,7 @@
         <v>1261</v>
       </c>
       <c r="G220" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H220">
         <v>1.7</v>
@@ -10323,7 +10413,7 @@
         <v>1261</v>
       </c>
       <c r="G221" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H221">
         <v>1.4</v>
@@ -10349,7 +10439,7 @@
         <v>1261</v>
       </c>
       <c r="G222" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H222">
         <v>2.8</v>
@@ -10372,10 +10462,10 @@
         <v>1258</v>
       </c>
       <c r="F223" t="s">
-        <v>1267</v>
+        <v>1278</v>
       </c>
       <c r="G223" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H223">
         <v>1.5</v>
@@ -10401,7 +10491,7 @@
         <v>1261</v>
       </c>
       <c r="G224" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H224">
         <v>0</v>
@@ -10427,7 +10517,7 @@
         <v>1261</v>
       </c>
       <c r="G225" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H225">
         <v>2.2</v>
@@ -10450,10 +10540,10 @@
         <v>1259</v>
       </c>
       <c r="F226" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G226" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -10479,7 +10569,7 @@
         <v>1261</v>
       </c>
       <c r="G227" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H227">
         <v>-3.1</v>
@@ -10505,7 +10595,7 @@
         <v>1261</v>
       </c>
       <c r="G228" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -10531,7 +10621,7 @@
         <v>1261</v>
       </c>
       <c r="G229" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H229">
         <v>2.6</v>
@@ -10557,7 +10647,7 @@
         <v>1261</v>
       </c>
       <c r="G230" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H230">
         <v>1.5</v>
@@ -10583,7 +10673,7 @@
         <v>1261</v>
       </c>
       <c r="G231" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -10609,7 +10699,7 @@
         <v>1261</v>
       </c>
       <c r="G232" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H232">
         <v>2.1</v>
@@ -10635,7 +10725,7 @@
         <v>1261</v>
       </c>
       <c r="G233" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H233">
         <v>-1.8</v>
@@ -10658,10 +10748,10 @@
         <v>1258</v>
       </c>
       <c r="F234" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="G234" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H234">
         <v>2.9</v>
@@ -10684,10 +10774,10 @@
         <v>1260</v>
       </c>
       <c r="F235" t="s">
-        <v>1265</v>
+        <v>1287</v>
       </c>
       <c r="G235" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H235">
         <v>-1.8</v>
@@ -10713,7 +10803,7 @@
         <v>1261</v>
       </c>
       <c r="G236" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H236">
         <v>1.7</v>
@@ -10739,7 +10829,7 @@
         <v>1261</v>
       </c>
       <c r="G237" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H237">
         <v>1.9</v>
@@ -10765,7 +10855,7 @@
         <v>1261</v>
       </c>
       <c r="G238" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H238">
         <v>1.8</v>
@@ -10791,7 +10881,7 @@
         <v>1262</v>
       </c>
       <c r="G239" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H239">
         <v>2.7</v>
@@ -10814,10 +10904,10 @@
         <v>1259</v>
       </c>
       <c r="F240" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G240" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -10840,10 +10930,10 @@
         <v>1259</v>
       </c>
       <c r="F241" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G241" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H241">
         <v>0</v>
@@ -10869,7 +10959,7 @@
         <v>1262</v>
       </c>
       <c r="G242" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H242">
         <v>2.9</v>
@@ -10895,7 +10985,7 @@
         <v>1261</v>
       </c>
       <c r="G243" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H243">
         <v>2.1</v>
@@ -10921,7 +11011,7 @@
         <v>1261</v>
       </c>
       <c r="G244" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H244">
         <v>2.5</v>
@@ -10947,7 +11037,7 @@
         <v>1262</v>
       </c>
       <c r="G245" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H245">
         <v>1.6</v>
@@ -10970,10 +11060,10 @@
         <v>1258</v>
       </c>
       <c r="F246" t="s">
-        <v>1263</v>
+        <v>1291</v>
       </c>
       <c r="G246" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H246">
         <v>1.2</v>
@@ -10999,7 +11089,7 @@
         <v>1262</v>
       </c>
       <c r="G247" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H247">
         <v>1.6</v>
@@ -11025,7 +11115,7 @@
         <v>1261</v>
       </c>
       <c r="G248" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H248">
         <v>-1.4</v>
@@ -11048,10 +11138,10 @@
         <v>1260</v>
       </c>
       <c r="F249" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="G249" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H249">
         <v>-1</v>
@@ -11074,10 +11164,10 @@
         <v>1260</v>
       </c>
       <c r="F250" t="s">
-        <v>1265</v>
+        <v>1292</v>
       </c>
       <c r="G250" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H250">
         <v>-0.7</v>
@@ -11100,10 +11190,10 @@
         <v>1258</v>
       </c>
       <c r="F251" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G251" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H251">
         <v>2.3</v>
@@ -11126,10 +11216,10 @@
         <v>1258</v>
       </c>
       <c r="F252" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G252" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H252">
         <v>1.7</v>
@@ -11152,10 +11242,10 @@
         <v>1260</v>
       </c>
       <c r="F253" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G253" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H253">
         <v>-1.8</v>
@@ -11178,10 +11268,10 @@
         <v>1260</v>
       </c>
       <c r="F254" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="G254" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H254">
         <v>-2.1</v>
@@ -11204,10 +11294,10 @@
         <v>1260</v>
       </c>
       <c r="F255" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="G255" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -11233,7 +11323,7 @@
         <v>1261</v>
       </c>
       <c r="G256" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -11259,7 +11349,7 @@
         <v>1261</v>
       </c>
       <c r="G257" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -11282,10 +11372,10 @@
         <v>1259</v>
       </c>
       <c r="F258" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G258" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -11311,7 +11401,7 @@
         <v>1261</v>
       </c>
       <c r="G259" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -11334,10 +11424,10 @@
         <v>1259</v>
       </c>
       <c r="F260" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G260" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -11363,7 +11453,7 @@
         <v>1261</v>
       </c>
       <c r="G261" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H261">
         <v>1.7</v>
@@ -11389,7 +11479,7 @@
         <v>1261</v>
       </c>
       <c r="G262" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H262">
         <v>2</v>
@@ -11415,7 +11505,7 @@
         <v>1261</v>
       </c>
       <c r="G263" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -11438,10 +11528,10 @@
         <v>1259</v>
       </c>
       <c r="F264" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G264" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -11467,7 +11557,7 @@
         <v>1261</v>
       </c>
       <c r="G265" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H265">
         <v>2.2</v>
@@ -11493,7 +11583,7 @@
         <v>1261</v>
       </c>
       <c r="G266" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H266">
         <v>0</v>
@@ -11519,7 +11609,7 @@
         <v>1261</v>
       </c>
       <c r="G267" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -11545,7 +11635,7 @@
         <v>1261</v>
       </c>
       <c r="G268" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -11571,7 +11661,7 @@
         <v>1261</v>
       </c>
       <c r="G269" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -11594,10 +11684,10 @@
         <v>1258</v>
       </c>
       <c r="F270" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G270" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H270">
         <v>2.3</v>
@@ -11620,10 +11710,10 @@
         <v>1258</v>
       </c>
       <c r="F271" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G271" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H271">
         <v>1.7</v>
@@ -11649,7 +11739,7 @@
         <v>1261</v>
       </c>
       <c r="G272" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -11675,7 +11765,7 @@
         <v>1261</v>
       </c>
       <c r="G273" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H273">
         <v>1.4</v>
@@ -11701,7 +11791,7 @@
         <v>1261</v>
       </c>
       <c r="G274" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H274">
         <v>-1.3</v>
@@ -11727,7 +11817,7 @@
         <v>1261</v>
       </c>
       <c r="G275" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H275">
         <v>-2.1</v>
@@ -11750,10 +11840,10 @@
         <v>1258</v>
       </c>
       <c r="F276" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G276" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H276">
         <v>2</v>
@@ -11776,10 +11866,10 @@
         <v>1258</v>
       </c>
       <c r="F277" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G277" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H277">
         <v>3</v>
@@ -11802,10 +11892,10 @@
         <v>1258</v>
       </c>
       <c r="F278" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G278" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H278">
         <v>2.5</v>
@@ -11831,7 +11921,7 @@
         <v>1261</v>
       </c>
       <c r="G279" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H279">
         <v>-1.5</v>
@@ -11857,7 +11947,7 @@
         <v>1261</v>
       </c>
       <c r="G280" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -11880,10 +11970,10 @@
         <v>1258</v>
       </c>
       <c r="F281" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G281" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H281">
         <v>1.5</v>
@@ -11909,7 +11999,7 @@
         <v>1261</v>
       </c>
       <c r="G282" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H282">
         <v>1.7</v>
@@ -11932,10 +12022,10 @@
         <v>1259</v>
       </c>
       <c r="F283" t="s">
-        <v>1265</v>
+        <v>1293</v>
       </c>
       <c r="G283" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -11961,7 +12051,7 @@
         <v>1261</v>
       </c>
       <c r="G284" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -11987,7 +12077,7 @@
         <v>1261</v>
       </c>
       <c r="G285" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H285">
         <v>0</v>
@@ -12010,10 +12100,10 @@
         <v>1260</v>
       </c>
       <c r="F286" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G286" t="s">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="H286">
         <v>-2.7</v>
@@ -12036,10 +12126,10 @@
         <v>1259</v>
       </c>
       <c r="F287" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G287" t="s">
-        <v>1272</v>
+        <v>1307</v>
       </c>
       <c r="H287">
         <v>0</v>
@@ -12062,10 +12152,10 @@
         <v>1260</v>
       </c>
       <c r="F288" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="G288" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H288">
         <v>-1.6</v>
@@ -12088,10 +12178,10 @@
         <v>1259</v>
       </c>
       <c r="F289" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G289" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H289">
         <v>0</v>
@@ -12114,10 +12204,10 @@
         <v>1259</v>
       </c>
       <c r="F290" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G290" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -12140,10 +12230,10 @@
         <v>1260</v>
       </c>
       <c r="F291" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G291" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H291">
         <v>-2.1</v>
@@ -12166,10 +12256,10 @@
         <v>1260</v>
       </c>
       <c r="F292" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G292" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H292">
         <v>-1.8</v>
@@ -12192,10 +12282,10 @@
         <v>1258</v>
       </c>
       <c r="F293" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G293" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H293">
         <v>2.2</v>
@@ -12218,10 +12308,10 @@
         <v>1259</v>
       </c>
       <c r="F294" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G294" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -12244,10 +12334,10 @@
         <v>1258</v>
       </c>
       <c r="F295" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G295" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H295">
         <v>2.4</v>
@@ -12270,10 +12360,10 @@
         <v>1259</v>
       </c>
       <c r="F296" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="G296" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H296">
         <v>0</v>
@@ -12296,10 +12386,10 @@
         <v>1259</v>
       </c>
       <c r="F297" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G297" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -12322,10 +12412,10 @@
         <v>1260</v>
       </c>
       <c r="F298" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G298" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H298">
         <v>-2.5</v>
@@ -12348,10 +12438,10 @@
         <v>1259</v>
       </c>
       <c r="F299" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G299" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H299">
         <v>0</v>
@@ -12374,10 +12464,10 @@
         <v>1258</v>
       </c>
       <c r="F300" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G300" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H300">
         <v>1.6</v>
@@ -12400,10 +12490,10 @@
         <v>1258</v>
       </c>
       <c r="F301" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G301" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H301">
         <v>2.3</v>
@@ -12426,10 +12516,10 @@
         <v>1260</v>
       </c>
       <c r="F302" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G302" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H302">
         <v>-1.3</v>
@@ -12452,10 +12542,10 @@
         <v>1260</v>
       </c>
       <c r="F303" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="G303" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H303">
         <v>-0.5</v>
@@ -12478,10 +12568,10 @@
         <v>1259</v>
       </c>
       <c r="F304" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G304" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -12504,10 +12594,10 @@
         <v>1260</v>
       </c>
       <c r="F305" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G305" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H305">
         <v>-2.2</v>
@@ -12530,10 +12620,10 @@
         <v>1259</v>
       </c>
       <c r="F306" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G306" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H306">
         <v>0</v>
@@ -12556,10 +12646,10 @@
         <v>1259</v>
       </c>
       <c r="F307" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G307" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -12582,10 +12672,10 @@
         <v>1259</v>
       </c>
       <c r="F308" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G308" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H308">
         <v>0</v>
@@ -12608,10 +12698,10 @@
         <v>1259</v>
       </c>
       <c r="F309" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G309" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H309">
         <v>0</v>
@@ -12634,10 +12724,10 @@
         <v>1259</v>
       </c>
       <c r="F310" t="s">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="G310" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H310">
         <v>0</v>
@@ -12660,10 +12750,10 @@
         <v>1258</v>
       </c>
       <c r="F311" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G311" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H311">
         <v>0.9</v>
@@ -12686,10 +12776,10 @@
         <v>1259</v>
       </c>
       <c r="F312" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G312" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H312">
         <v>0</v>
@@ -12712,10 +12802,10 @@
         <v>1258</v>
       </c>
       <c r="F313" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G313" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H313">
         <v>2.8</v>
@@ -12738,10 +12828,10 @@
         <v>1259</v>
       </c>
       <c r="F314" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G314" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -12764,10 +12854,10 @@
         <v>1259</v>
       </c>
       <c r="F315" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G315" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -12790,10 +12880,10 @@
         <v>1258</v>
       </c>
       <c r="F316" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G316" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H316">
         <v>2.5</v>
@@ -12816,10 +12906,10 @@
         <v>1258</v>
       </c>
       <c r="F317" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G317" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H317">
         <v>1.6</v>
@@ -12842,10 +12932,10 @@
         <v>1259</v>
       </c>
       <c r="F318" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G318" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H318">
         <v>0</v>
@@ -12868,10 +12958,10 @@
         <v>1259</v>
       </c>
       <c r="F319" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G319" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H319">
         <v>0</v>
@@ -12894,10 +12984,10 @@
         <v>1259</v>
       </c>
       <c r="F320" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G320" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -12920,10 +13010,10 @@
         <v>1258</v>
       </c>
       <c r="F321" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G321" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H321">
         <v>2.2</v>
@@ -12946,10 +13036,10 @@
         <v>1259</v>
       </c>
       <c r="F322" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G322" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H322">
         <v>0</v>
@@ -12972,10 +13062,10 @@
         <v>1259</v>
       </c>
       <c r="F323" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G323" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H323">
         <v>0</v>
@@ -12998,10 +13088,10 @@
         <v>1259</v>
       </c>
       <c r="F324" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G324" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -13024,10 +13114,10 @@
         <v>1259</v>
       </c>
       <c r="F325" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G325" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -13050,10 +13140,10 @@
         <v>1259</v>
       </c>
       <c r="F326" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G326" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H326">
         <v>0</v>
@@ -13076,10 +13166,10 @@
         <v>1259</v>
       </c>
       <c r="F327" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G327" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -13102,10 +13192,10 @@
         <v>1259</v>
       </c>
       <c r="F328" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G328" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H328">
         <v>0</v>
@@ -13128,10 +13218,10 @@
         <v>1258</v>
       </c>
       <c r="F329" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G329" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H329">
         <v>1.3</v>
@@ -13154,10 +13244,10 @@
         <v>1259</v>
       </c>
       <c r="F330" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="G330" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H330">
         <v>0</v>
@@ -13180,10 +13270,10 @@
         <v>1258</v>
       </c>
       <c r="F331" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="G331" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H331">
         <v>1.8</v>
@@ -13206,10 +13296,10 @@
         <v>1258</v>
       </c>
       <c r="F332" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G332" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H332">
         <v>1.5</v>
@@ -13232,10 +13322,10 @@
         <v>1258</v>
       </c>
       <c r="F333" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="G333" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H333">
         <v>2.2</v>
@@ -13258,10 +13348,10 @@
         <v>1258</v>
       </c>
       <c r="F334" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G334" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H334">
         <v>1.7</v>
@@ -13284,10 +13374,10 @@
         <v>1258</v>
       </c>
       <c r="F335" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G335" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H335">
         <v>2</v>
@@ -13310,10 +13400,10 @@
         <v>1258</v>
       </c>
       <c r="F336" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G336" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H336">
         <v>1.8</v>
@@ -13336,10 +13426,10 @@
         <v>1260</v>
       </c>
       <c r="F337" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G337" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H337">
         <v>-2.4</v>
@@ -13362,10 +13452,10 @@
         <v>1258</v>
       </c>
       <c r="F338" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G338" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H338">
         <v>2.5</v>
@@ -13388,10 +13478,10 @@
         <v>1259</v>
       </c>
       <c r="F339" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G339" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H339">
         <v>0</v>
@@ -13414,10 +13504,10 @@
         <v>1258</v>
       </c>
       <c r="F340" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G340" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H340">
         <v>1.7</v>
@@ -13440,10 +13530,10 @@
         <v>1258</v>
       </c>
       <c r="F341" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G341" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H341">
         <v>1.8</v>
@@ -13466,10 +13556,10 @@
         <v>1258</v>
       </c>
       <c r="F342" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="G342" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H342">
         <v>2.1</v>
@@ -13492,10 +13582,10 @@
         <v>1258</v>
       </c>
       <c r="F343" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G343" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H343">
         <v>1.8</v>
@@ -13518,10 +13608,10 @@
         <v>1258</v>
       </c>
       <c r="F344" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="G344" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H344">
         <v>0.2</v>
@@ -13544,10 +13634,10 @@
         <v>1258</v>
       </c>
       <c r="F345" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G345" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H345">
         <v>2.1</v>
@@ -13570,10 +13660,10 @@
         <v>1258</v>
       </c>
       <c r="F346" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G346" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H346">
         <v>1.9</v>
@@ -13596,10 +13686,10 @@
         <v>1260</v>
       </c>
       <c r="F347" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="G347" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H347">
         <v>-1.8</v>
@@ -13622,10 +13712,10 @@
         <v>1259</v>
       </c>
       <c r="F348" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G348" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -13648,10 +13738,10 @@
         <v>1260</v>
       </c>
       <c r="F349" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="G349" t="s">
-        <v>1273</v>
+        <v>1307</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -13674,10 +13764,10 @@
         <v>1260</v>
       </c>
       <c r="F350" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G350" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H350">
         <v>-1.7</v>
@@ -13700,10 +13790,10 @@
         <v>1259</v>
       </c>
       <c r="F351" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="G351" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H351">
         <v>0</v>
@@ -13726,10 +13816,10 @@
         <v>1258</v>
       </c>
       <c r="F352" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G352" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H352">
         <v>2.9</v>
@@ -13752,10 +13842,10 @@
         <v>1259</v>
       </c>
       <c r="F353" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G353" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H353">
         <v>0</v>
@@ -13778,10 +13868,10 @@
         <v>1259</v>
       </c>
       <c r="F354" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="G354" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H354">
         <v>0</v>
@@ -13804,10 +13894,10 @@
         <v>1260</v>
       </c>
       <c r="F355" t="s">
-        <v>1265</v>
+        <v>1294</v>
       </c>
       <c r="G355" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H355">
         <v>-1.2</v>
@@ -13830,10 +13920,10 @@
         <v>1258</v>
       </c>
       <c r="F356" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
       <c r="G356" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H356">
         <v>1.9</v>
@@ -13856,10 +13946,10 @@
         <v>1258</v>
       </c>
       <c r="F357" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="G357" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H357">
         <v>1.7</v>
@@ -13882,10 +13972,10 @@
         <v>1258</v>
       </c>
       <c r="F358" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G358" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H358">
         <v>2</v>
@@ -13908,10 +13998,10 @@
         <v>1260</v>
       </c>
       <c r="F359" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="G359" t="s">
-        <v>1273</v>
+        <v>1308</v>
       </c>
       <c r="H359">
         <v>-2.3</v>
@@ -13934,10 +14024,10 @@
         <v>1258</v>
       </c>
       <c r="F360" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G360" t="s">
-        <v>1274</v>
+        <v>1309</v>
       </c>
       <c r="H360">
         <v>2</v>
@@ -13960,10 +14050,10 @@
         <v>1259</v>
       </c>
       <c r="F361" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G361" t="s">
-        <v>1275</v>
+        <v>1310</v>
       </c>
       <c r="H361">
         <v>0</v>
@@ -13986,10 +14076,10 @@
         <v>1260</v>
       </c>
       <c r="F362" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="G362" t="s">
-        <v>1276</v>
+        <v>1311</v>
       </c>
       <c r="H362">
         <v>-1.7</v>
@@ -14012,10 +14102,10 @@
         <v>1259</v>
       </c>
       <c r="F363" t="s">
-        <v>1266</v>
+        <v>1295</v>
       </c>
       <c r="G363" t="s">
-        <v>1277</v>
+        <v>1312</v>
       </c>
       <c r="H363">
         <v>0</v>
@@ -14038,10 +14128,10 @@
         <v>1260</v>
       </c>
       <c r="F364" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G364" t="s">
-        <v>1278</v>
+        <v>1313</v>
       </c>
       <c r="H364">
         <v>-2</v>
@@ -14064,10 +14154,10 @@
         <v>1259</v>
       </c>
       <c r="F365" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G365" t="s">
-        <v>1279</v>
+        <v>1307</v>
       </c>
       <c r="H365">
         <v>0</v>
@@ -14090,10 +14180,10 @@
         <v>1259</v>
       </c>
       <c r="F366" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G366" t="s">
-        <v>1280</v>
+        <v>1314</v>
       </c>
       <c r="H366">
         <v>0</v>
@@ -14116,10 +14206,10 @@
         <v>1258</v>
       </c>
       <c r="F367" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G367" t="s">
-        <v>1281</v>
+        <v>1315</v>
       </c>
       <c r="H367">
         <v>2.6</v>
@@ -14142,10 +14232,10 @@
         <v>1258</v>
       </c>
       <c r="F368" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G368" t="s">
-        <v>1282</v>
+        <v>1316</v>
       </c>
       <c r="H368">
         <v>2.6</v>
@@ -14168,10 +14258,10 @@
         <v>1258</v>
       </c>
       <c r="F369" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G369" t="s">
-        <v>1283</v>
+        <v>1317</v>
       </c>
       <c r="H369">
         <v>1.9</v>
@@ -14194,10 +14284,10 @@
         <v>1260</v>
       </c>
       <c r="F370" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G370" t="s">
-        <v>1284</v>
+        <v>1318</v>
       </c>
       <c r="H370">
         <v>-2.1</v>
@@ -14220,10 +14310,10 @@
         <v>1258</v>
       </c>
       <c r="F371" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G371" t="s">
-        <v>1285</v>
+        <v>1319</v>
       </c>
       <c r="H371">
         <v>2.1</v>
@@ -14246,10 +14336,10 @@
         <v>1259</v>
       </c>
       <c r="F372" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G372" t="s">
-        <v>1286</v>
+        <v>1320</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -14272,10 +14362,10 @@
         <v>1259</v>
       </c>
       <c r="F373" t="s">
-        <v>1265</v>
+        <v>1297</v>
       </c>
       <c r="G373" t="s">
-        <v>1287</v>
+        <v>1321</v>
       </c>
       <c r="H373">
         <v>0</v>
@@ -14298,10 +14388,10 @@
         <v>1259</v>
       </c>
       <c r="F374" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G374" t="s">
-        <v>1288</v>
+        <v>1322</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -14324,10 +14414,10 @@
         <v>1260</v>
       </c>
       <c r="F375" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G375" t="s">
-        <v>1289</v>
+        <v>1323</v>
       </c>
       <c r="H375">
         <v>-1.9</v>
@@ -14350,10 +14440,10 @@
         <v>1260</v>
       </c>
       <c r="F376" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G376" t="s">
-        <v>1290</v>
+        <v>1324</v>
       </c>
       <c r="H376">
         <v>-1.3</v>
@@ -14376,10 +14466,10 @@
         <v>1259</v>
       </c>
       <c r="F377" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G377" t="s">
-        <v>1291</v>
+        <v>1325</v>
       </c>
       <c r="H377">
         <v>0</v>
@@ -14402,10 +14492,10 @@
         <v>1260</v>
       </c>
       <c r="F378" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G378" t="s">
-        <v>1292</v>
+        <v>1326</v>
       </c>
       <c r="H378">
         <v>-0.6</v>
@@ -14428,10 +14518,10 @@
         <v>1259</v>
       </c>
       <c r="F379" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G379" t="s">
-        <v>1293</v>
+        <v>1327</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -14454,10 +14544,10 @@
         <v>1258</v>
       </c>
       <c r="F380" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G380" t="s">
-        <v>1294</v>
+        <v>1328</v>
       </c>
       <c r="H380">
         <v>2.4</v>
@@ -14480,10 +14570,10 @@
         <v>1260</v>
       </c>
       <c r="F381" t="s">
-        <v>1265</v>
+        <v>1298</v>
       </c>
       <c r="G381" t="s">
-        <v>1295</v>
+        <v>1329</v>
       </c>
       <c r="H381">
         <v>-1.6</v>
@@ -14506,10 +14596,10 @@
         <v>1258</v>
       </c>
       <c r="F382" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G382" t="s">
-        <v>1296</v>
+        <v>1330</v>
       </c>
       <c r="H382">
         <v>2.7</v>
@@ -14532,10 +14622,10 @@
         <v>1258</v>
       </c>
       <c r="F383" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G383" t="s">
-        <v>1297</v>
+        <v>1331</v>
       </c>
       <c r="H383">
         <v>1.7</v>
@@ -14558,10 +14648,10 @@
         <v>1258</v>
       </c>
       <c r="F384" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G384" t="s">
-        <v>1298</v>
+        <v>1332</v>
       </c>
       <c r="H384">
         <v>1.3</v>
@@ -14587,7 +14677,7 @@
         <v>1262</v>
       </c>
       <c r="G385" t="s">
-        <v>1299</v>
+        <v>1333</v>
       </c>
       <c r="H385">
         <v>2.4</v>
@@ -14610,10 +14700,10 @@
         <v>1259</v>
       </c>
       <c r="F386" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G386" t="s">
-        <v>1300</v>
+        <v>1334</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -14636,10 +14726,10 @@
         <v>1260</v>
       </c>
       <c r="F387" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G387" t="s">
-        <v>1301</v>
+        <v>1335</v>
       </c>
       <c r="H387">
         <v>-1.1</v>
@@ -14662,10 +14752,10 @@
         <v>1259</v>
       </c>
       <c r="F388" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G388" t="s">
-        <v>1302</v>
+        <v>1336</v>
       </c>
       <c r="H388">
         <v>0</v>
@@ -14688,10 +14778,10 @@
         <v>1259</v>
       </c>
       <c r="F389" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G389" t="s">
-        <v>1303</v>
+        <v>1337</v>
       </c>
       <c r="H389">
         <v>0</v>
@@ -14714,10 +14804,10 @@
         <v>1259</v>
       </c>
       <c r="F390" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G390" t="s">
-        <v>1304</v>
+        <v>1338</v>
       </c>
       <c r="H390">
         <v>0</v>
@@ -14740,10 +14830,10 @@
         <v>1259</v>
       </c>
       <c r="F391" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G391" t="s">
-        <v>1305</v>
+        <v>1339</v>
       </c>
       <c r="H391">
         <v>0</v>
@@ -14766,10 +14856,10 @@
         <v>1258</v>
       </c>
       <c r="F392" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G392" t="s">
-        <v>1306</v>
+        <v>1340</v>
       </c>
       <c r="H392">
         <v>2</v>
@@ -14792,10 +14882,10 @@
         <v>1259</v>
       </c>
       <c r="F393" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G393" t="s">
-        <v>1307</v>
+        <v>1341</v>
       </c>
       <c r="H393">
         <v>0</v>
@@ -14818,10 +14908,10 @@
         <v>1259</v>
       </c>
       <c r="F394" t="s">
-        <v>1265</v>
+        <v>1299</v>
       </c>
       <c r="G394" t="s">
-        <v>1308</v>
+        <v>1342</v>
       </c>
       <c r="H394">
         <v>0</v>
@@ -14844,10 +14934,10 @@
         <v>1258</v>
       </c>
       <c r="F395" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="G395" t="s">
-        <v>1309</v>
+        <v>1343</v>
       </c>
       <c r="H395">
         <v>1.1</v>
@@ -14870,10 +14960,10 @@
         <v>1259</v>
       </c>
       <c r="F396" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G396" t="s">
-        <v>1310</v>
+        <v>1344</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -14896,10 +14986,10 @@
         <v>1259</v>
       </c>
       <c r="F397" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G397" t="s">
-        <v>1311</v>
+        <v>1345</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -14922,10 +15012,10 @@
         <v>1259</v>
       </c>
       <c r="F398" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G398" t="s">
-        <v>1312</v>
+        <v>1346</v>
       </c>
       <c r="H398">
         <v>0</v>
@@ -14948,10 +15038,10 @@
         <v>1258</v>
       </c>
       <c r="F399" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G399" t="s">
-        <v>1313</v>
+        <v>1347</v>
       </c>
       <c r="H399">
         <v>2.4</v>
@@ -14974,10 +15064,10 @@
         <v>1260</v>
       </c>
       <c r="F400" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G400" t="s">
-        <v>1314</v>
+        <v>1348</v>
       </c>
       <c r="H400">
         <v>-1.2</v>
@@ -15000,10 +15090,10 @@
         <v>1260</v>
       </c>
       <c r="F401" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G401" t="s">
-        <v>1315</v>
+        <v>1349</v>
       </c>
       <c r="H401">
         <v>-2.2</v>
@@ -15026,10 +15116,10 @@
         <v>1258</v>
       </c>
       <c r="F402" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G402" t="s">
-        <v>1316</v>
+        <v>1350</v>
       </c>
       <c r="H402">
         <v>1.3</v>
@@ -15052,10 +15142,10 @@
         <v>1259</v>
       </c>
       <c r="F403" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G403" t="s">
-        <v>1317</v>
+        <v>1351</v>
       </c>
       <c r="H403">
         <v>0</v>
@@ -15078,10 +15168,10 @@
         <v>1258</v>
       </c>
       <c r="F404" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G404" t="s">
-        <v>1318</v>
+        <v>1352</v>
       </c>
       <c r="H404">
         <v>2.1</v>
@@ -15104,10 +15194,10 @@
         <v>1259</v>
       </c>
       <c r="F405" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G405" t="s">
-        <v>1319</v>
+        <v>1353</v>
       </c>
       <c r="H405">
         <v>0</v>
@@ -15130,10 +15220,10 @@
         <v>1260</v>
       </c>
       <c r="F406" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G406" t="s">
-        <v>1320</v>
+        <v>1354</v>
       </c>
       <c r="H406">
         <v>-2</v>
@@ -15156,10 +15246,10 @@
         <v>1259</v>
       </c>
       <c r="F407" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G407" t="s">
-        <v>1321</v>
+        <v>1307</v>
       </c>
       <c r="H407">
         <v>0</v>
@@ -15182,10 +15272,10 @@
         <v>1260</v>
       </c>
       <c r="F408" t="s">
-        <v>1265</v>
+        <v>1300</v>
       </c>
       <c r="G408" t="s">
-        <v>1322</v>
+        <v>1355</v>
       </c>
       <c r="H408">
         <v>-0.4</v>
@@ -15208,10 +15298,10 @@
         <v>1259</v>
       </c>
       <c r="F409" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G409" t="s">
-        <v>1323</v>
+        <v>1356</v>
       </c>
       <c r="H409">
         <v>0</v>
@@ -15234,10 +15324,10 @@
         <v>1259</v>
       </c>
       <c r="F410" t="s">
-        <v>1262</v>
+        <v>1301</v>
       </c>
       <c r="G410" t="s">
-        <v>1324</v>
+        <v>1357</v>
       </c>
       <c r="H410">
         <v>0</v>
@@ -15260,10 +15350,10 @@
         <v>1259</v>
       </c>
       <c r="F411" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G411" t="s">
-        <v>1325</v>
+        <v>1358</v>
       </c>
       <c r="H411">
         <v>0</v>
@@ -15286,10 +15376,10 @@
         <v>1258</v>
       </c>
       <c r="F412" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="G412" t="s">
-        <v>1326</v>
+        <v>1359</v>
       </c>
       <c r="H412">
         <v>2.7</v>
@@ -15312,10 +15402,10 @@
         <v>1260</v>
       </c>
       <c r="F413" t="s">
-        <v>1270</v>
+        <v>1302</v>
       </c>
       <c r="G413" t="s">
-        <v>1327</v>
+        <v>1360</v>
       </c>
       <c r="H413">
         <v>-2</v>
@@ -15338,10 +15428,10 @@
         <v>1258</v>
       </c>
       <c r="F414" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G414" t="s">
-        <v>1328</v>
+        <v>1361</v>
       </c>
       <c r="H414">
         <v>1.8</v>
@@ -15364,10 +15454,10 @@
         <v>1258</v>
       </c>
       <c r="F415" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G415" t="s">
-        <v>1329</v>
+        <v>1362</v>
       </c>
       <c r="H415">
         <v>2</v>
@@ -15390,10 +15480,10 @@
         <v>1258</v>
       </c>
       <c r="F416" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G416" t="s">
-        <v>1330</v>
+        <v>1363</v>
       </c>
       <c r="H416">
         <v>2</v>
@@ -15416,10 +15506,10 @@
         <v>1258</v>
       </c>
       <c r="F417" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G417" t="s">
-        <v>1331</v>
+        <v>1364</v>
       </c>
       <c r="H417">
         <v>0.6</v>
@@ -15442,10 +15532,10 @@
         <v>1258</v>
       </c>
       <c r="F418" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G418" t="s">
-        <v>1332</v>
+        <v>1365</v>
       </c>
       <c r="H418">
         <v>2.3</v>
@@ -15468,10 +15558,10 @@
         <v>1259</v>
       </c>
       <c r="F419" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G419" t="s">
-        <v>1333</v>
+        <v>1366</v>
       </c>
       <c r="H419">
         <v>0</v>
@@ -15494,10 +15584,10 @@
         <v>1260</v>
       </c>
       <c r="F420" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G420" t="s">
-        <v>1334</v>
+        <v>1367</v>
       </c>
       <c r="H420">
         <v>-2.1</v>
@@ -15520,10 +15610,10 @@
         <v>1259</v>
       </c>
       <c r="F421" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G421" t="s">
-        <v>1335</v>
+        <v>1368</v>
       </c>
       <c r="H421">
         <v>0</v>
@@ -15546,10 +15636,10 @@
         <v>1260</v>
       </c>
       <c r="F422" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G422" t="s">
-        <v>1336</v>
+        <v>1369</v>
       </c>
       <c r="H422">
         <v>-2.6</v>
@@ -15572,10 +15662,10 @@
         <v>1259</v>
       </c>
       <c r="F423" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G423" t="s">
-        <v>1337</v>
+        <v>1370</v>
       </c>
       <c r="H423">
         <v>0</v>
@@ -15598,10 +15688,10 @@
         <v>1259</v>
       </c>
       <c r="F424" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G424" t="s">
-        <v>1338</v>
+        <v>1371</v>
       </c>
       <c r="H424">
         <v>0</v>
@@ -15624,10 +15714,10 @@
         <v>1260</v>
       </c>
       <c r="F425" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G425" t="s">
-        <v>1339</v>
+        <v>1372</v>
       </c>
       <c r="H425">
         <v>-2.2</v>
@@ -15650,10 +15740,10 @@
         <v>1259</v>
       </c>
       <c r="F426" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G426" t="s">
-        <v>1340</v>
+        <v>1373</v>
       </c>
       <c r="H426">
         <v>0</v>
@@ -15676,10 +15766,10 @@
         <v>1259</v>
       </c>
       <c r="F427" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G427" t="s">
-        <v>1341</v>
+        <v>1374</v>
       </c>
       <c r="H427">
         <v>0</v>
@@ -15702,10 +15792,10 @@
         <v>1258</v>
       </c>
       <c r="F428" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G428" t="s">
-        <v>1342</v>
+        <v>1375</v>
       </c>
       <c r="H428">
         <v>2.1</v>
@@ -15728,10 +15818,10 @@
         <v>1259</v>
       </c>
       <c r="F429" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G429" t="s">
-        <v>1343</v>
+        <v>1307</v>
       </c>
       <c r="H429">
         <v>0</v>
@@ -15754,10 +15844,10 @@
         <v>1258</v>
       </c>
       <c r="F430" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G430" t="s">
-        <v>1344</v>
+        <v>1376</v>
       </c>
       <c r="H430">
         <v>2.1</v>
@@ -15780,10 +15870,10 @@
         <v>1260</v>
       </c>
       <c r="F431" t="s">
-        <v>1270</v>
+        <v>1302</v>
       </c>
       <c r="G431" t="s">
-        <v>1345</v>
+        <v>1377</v>
       </c>
       <c r="H431">
         <v>-1.6</v>
@@ -15806,10 +15896,10 @@
         <v>1260</v>
       </c>
       <c r="F432" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G432" t="s">
-        <v>1346</v>
+        <v>1378</v>
       </c>
       <c r="H432">
         <v>-0.6</v>
@@ -15832,10 +15922,10 @@
         <v>1259</v>
       </c>
       <c r="F433" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G433" t="s">
-        <v>1347</v>
+        <v>1379</v>
       </c>
       <c r="H433">
         <v>0</v>
@@ -15858,10 +15948,10 @@
         <v>1259</v>
       </c>
       <c r="F434" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G434" t="s">
-        <v>1348</v>
+        <v>1380</v>
       </c>
       <c r="H434">
         <v>0</v>
@@ -15884,10 +15974,10 @@
         <v>1258</v>
       </c>
       <c r="F435" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G435" t="s">
-        <v>1349</v>
+        <v>1381</v>
       </c>
       <c r="H435">
         <v>2.4</v>
@@ -15910,10 +16000,10 @@
         <v>1260</v>
       </c>
       <c r="F436" t="s">
-        <v>1265</v>
+        <v>1300</v>
       </c>
       <c r="G436" t="s">
-        <v>1350</v>
+        <v>1382</v>
       </c>
       <c r="H436">
         <v>-1.5</v>
@@ -15936,10 +16026,10 @@
         <v>1259</v>
       </c>
       <c r="F437" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G437" t="s">
-        <v>1351</v>
+        <v>1383</v>
       </c>
       <c r="H437">
         <v>0</v>
@@ -15962,10 +16052,10 @@
         <v>1260</v>
       </c>
       <c r="F438" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G438" t="s">
-        <v>1352</v>
+        <v>1384</v>
       </c>
       <c r="H438">
         <v>-1.3</v>
@@ -15988,10 +16078,10 @@
         <v>1259</v>
       </c>
       <c r="F439" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G439" t="s">
-        <v>1353</v>
+        <v>1385</v>
       </c>
       <c r="H439">
         <v>0</v>
@@ -16014,10 +16104,10 @@
         <v>1259</v>
       </c>
       <c r="F440" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G440" t="s">
-        <v>1354</v>
+        <v>1386</v>
       </c>
       <c r="H440">
         <v>0</v>
@@ -16040,10 +16130,10 @@
         <v>1258</v>
       </c>
       <c r="F441" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G441" t="s">
-        <v>1355</v>
+        <v>1387</v>
       </c>
       <c r="H441">
         <v>1.8</v>
@@ -16066,10 +16156,10 @@
         <v>1260</v>
       </c>
       <c r="F442" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="G442" t="s">
-        <v>1356</v>
+        <v>1388</v>
       </c>
       <c r="H442">
         <v>-2.1</v>
@@ -16092,10 +16182,10 @@
         <v>1260</v>
       </c>
       <c r="F443" t="s">
-        <v>1265</v>
+        <v>1300</v>
       </c>
       <c r="G443" t="s">
-        <v>1357</v>
+        <v>1389</v>
       </c>
       <c r="H443">
         <v>-1.9</v>
@@ -16118,10 +16208,10 @@
         <v>1259</v>
       </c>
       <c r="F444" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="G444" t="s">
-        <v>1358</v>
+        <v>1390</v>
       </c>
       <c r="H444">
         <v>0</v>
@@ -16144,10 +16234,10 @@
         <v>1260</v>
       </c>
       <c r="F445" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="G445" t="s">
-        <v>1359</v>
+        <v>1391</v>
       </c>
       <c r="H445">
         <v>-1.5</v>
@@ -16170,10 +16260,10 @@
         <v>1260</v>
       </c>
       <c r="F446" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G446" t="s">
-        <v>1360</v>
+        <v>1392</v>
       </c>
       <c r="H446">
         <v>-2.1</v>
@@ -16196,10 +16286,10 @@
         <v>1258</v>
       </c>
       <c r="F447" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G447" t="s">
-        <v>1361</v>
+        <v>1393</v>
       </c>
       <c r="H447">
         <v>2.3</v>
@@ -16222,10 +16312,10 @@
         <v>1260</v>
       </c>
       <c r="F448" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G448" t="s">
-        <v>1362</v>
+        <v>1394</v>
       </c>
       <c r="H448">
         <v>-1.6</v>
@@ -16248,10 +16338,10 @@
         <v>1260</v>
       </c>
       <c r="F449" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G449" t="s">
-        <v>1363</v>
+        <v>1395</v>
       </c>
       <c r="H449">
         <v>-0.8</v>
@@ -16274,10 +16364,10 @@
         <v>1259</v>
       </c>
       <c r="F450" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G450" t="s">
-        <v>1364</v>
+        <v>1396</v>
       </c>
       <c r="H450">
         <v>0</v>
@@ -16300,10 +16390,10 @@
         <v>1260</v>
       </c>
       <c r="F451" t="s">
-        <v>1270</v>
+        <v>1302</v>
       </c>
       <c r="G451" t="s">
-        <v>1365</v>
+        <v>1397</v>
       </c>
       <c r="H451">
         <v>-1.5</v>
@@ -16326,10 +16416,10 @@
         <v>1260</v>
       </c>
       <c r="F452" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G452" t="s">
-        <v>1366</v>
+        <v>1398</v>
       </c>
       <c r="H452">
         <v>-2.2</v>
@@ -16352,10 +16442,10 @@
         <v>1259</v>
       </c>
       <c r="F453" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G453" t="s">
-        <v>1367</v>
+        <v>1399</v>
       </c>
       <c r="H453">
         <v>0</v>
@@ -16378,10 +16468,10 @@
         <v>1258</v>
       </c>
       <c r="F454" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G454" t="s">
-        <v>1368</v>
+        <v>1400</v>
       </c>
       <c r="H454">
         <v>1.6</v>
@@ -16404,10 +16494,10 @@
         <v>1260</v>
       </c>
       <c r="F455" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G455" t="s">
-        <v>1369</v>
+        <v>1401</v>
       </c>
       <c r="H455">
         <v>-2.2</v>
@@ -16430,10 +16520,10 @@
         <v>1260</v>
       </c>
       <c r="F456" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G456" t="s">
-        <v>1370</v>
+        <v>1402</v>
       </c>
       <c r="H456">
         <v>-1.8</v>
@@ -16456,10 +16546,10 @@
         <v>1260</v>
       </c>
       <c r="F457" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="G457" t="s">
-        <v>1371</v>
+        <v>1403</v>
       </c>
       <c r="H457">
         <v>-2.1</v>
@@ -16482,10 +16572,10 @@
         <v>1258</v>
       </c>
       <c r="F458" t="s">
-        <v>1262</v>
+        <v>1303</v>
       </c>
       <c r="G458" t="s">
-        <v>1372</v>
+        <v>1404</v>
       </c>
       <c r="H458">
         <v>1.8</v>
@@ -16508,10 +16598,10 @@
         <v>1260</v>
       </c>
       <c r="F459" t="s">
-        <v>1265</v>
+        <v>1287</v>
       </c>
       <c r="G459" t="s">
-        <v>1373</v>
+        <v>1405</v>
       </c>
       <c r="H459">
         <v>-1.4</v>
@@ -16534,10 +16624,10 @@
         <v>1260</v>
       </c>
       <c r="F460" t="s">
-        <v>1270</v>
+        <v>1304</v>
       </c>
       <c r="G460" t="s">
-        <v>1374</v>
+        <v>1406</v>
       </c>
       <c r="H460">
         <v>-0.7</v>
@@ -16560,10 +16650,10 @@
         <v>1260</v>
       </c>
       <c r="F461" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G461" t="s">
-        <v>1375</v>
+        <v>1407</v>
       </c>
       <c r="H461">
         <v>-1.9</v>
@@ -16586,10 +16676,10 @@
         <v>1260</v>
       </c>
       <c r="F462" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="G462" t="s">
-        <v>1376</v>
+        <v>1408</v>
       </c>
       <c r="H462">
         <v>-2.3</v>
@@ -16612,10 +16702,10 @@
         <v>1258</v>
       </c>
       <c r="F463" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="G463" t="s">
-        <v>1377</v>
+        <v>1409</v>
       </c>
       <c r="H463">
         <v>2.2</v>
@@ -16638,10 +16728,10 @@
         <v>1258</v>
       </c>
       <c r="F464" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="G464" t="s">
-        <v>1378</v>
+        <v>1410</v>
       </c>
       <c r="H464">
         <v>2.3</v>
@@ -16664,10 +16754,10 @@
         <v>1260</v>
       </c>
       <c r="F465" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G465" t="s">
-        <v>1379</v>
+        <v>1411</v>
       </c>
       <c r="H465">
         <v>-1.4</v>
@@ -16690,10 +16780,10 @@
         <v>1259</v>
       </c>
       <c r="F466" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G466" t="s">
-        <v>1380</v>
+        <v>1412</v>
       </c>
       <c r="H466">
         <v>0</v>
@@ -16716,10 +16806,10 @@
         <v>1258</v>
       </c>
       <c r="F467" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G467" t="s">
-        <v>1381</v>
+        <v>1413</v>
       </c>
       <c r="H467">
         <v>1.7</v>
@@ -16742,10 +16832,10 @@
         <v>1258</v>
       </c>
       <c r="F468" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G468" t="s">
-        <v>1382</v>
+        <v>1414</v>
       </c>
       <c r="H468">
         <v>2.6</v>
@@ -16768,10 +16858,10 @@
         <v>1258</v>
       </c>
       <c r="F469" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G469" t="s">
-        <v>1383</v>
+        <v>1415</v>
       </c>
       <c r="H469">
         <v>1.3</v>
@@ -16794,10 +16884,10 @@
         <v>1260</v>
       </c>
       <c r="F470" t="s">
-        <v>1265</v>
+        <v>1285</v>
       </c>
       <c r="G470" t="s">
-        <v>1384</v>
+        <v>1416</v>
       </c>
       <c r="H470">
         <v>-1.2</v>
@@ -16820,10 +16910,10 @@
         <v>1258</v>
       </c>
       <c r="F471" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G471" t="s">
-        <v>1385</v>
+        <v>1417</v>
       </c>
       <c r="H471">
         <v>1.9</v>
@@ -16846,10 +16936,10 @@
         <v>1258</v>
       </c>
       <c r="F472" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G472" t="s">
-        <v>1386</v>
+        <v>1418</v>
       </c>
       <c r="H472">
         <v>1.6</v>
@@ -16872,10 +16962,10 @@
         <v>1260</v>
       </c>
       <c r="F473" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G473" t="s">
-        <v>1387</v>
+        <v>1419</v>
       </c>
       <c r="H473">
         <v>-1.1</v>
@@ -16898,10 +16988,10 @@
         <v>1258</v>
       </c>
       <c r="F474" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G474" t="s">
-        <v>1388</v>
+        <v>1420</v>
       </c>
       <c r="H474">
         <v>1.5</v>
@@ -16924,10 +17014,10 @@
         <v>1258</v>
       </c>
       <c r="F475" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G475" t="s">
-        <v>1389</v>
+        <v>1421</v>
       </c>
       <c r="H475">
         <v>2.3</v>
@@ -16953,7 +17043,7 @@
         <v>1262</v>
       </c>
       <c r="G476" t="s">
-        <v>1390</v>
+        <v>1422</v>
       </c>
       <c r="H476">
         <v>1.9</v>
@@ -16976,10 +17066,10 @@
         <v>1259</v>
       </c>
       <c r="F477" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G477" t="s">
-        <v>1391</v>
+        <v>1423</v>
       </c>
       <c r="H477">
         <v>0</v>
@@ -17005,7 +17095,7 @@
         <v>1262</v>
       </c>
       <c r="G478" t="s">
-        <v>1392</v>
+        <v>1424</v>
       </c>
       <c r="H478">
         <v>2.3</v>
@@ -17028,10 +17118,10 @@
         <v>1258</v>
       </c>
       <c r="F479" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G479" t="s">
-        <v>1393</v>
+        <v>1425</v>
       </c>
       <c r="H479">
         <v>2.1</v>
@@ -17054,10 +17144,10 @@
         <v>1259</v>
       </c>
       <c r="F480" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G480" t="s">
-        <v>1394</v>
+        <v>1307</v>
       </c>
       <c r="H480">
         <v>0</v>
@@ -17080,10 +17170,10 @@
         <v>1260</v>
       </c>
       <c r="F481" t="s">
-        <v>1265</v>
+        <v>1282</v>
       </c>
       <c r="G481" t="s">
-        <v>1395</v>
+        <v>1426</v>
       </c>
       <c r="H481">
         <v>-1</v>
@@ -17106,10 +17196,10 @@
         <v>1258</v>
       </c>
       <c r="F482" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G482" t="s">
-        <v>1396</v>
+        <v>1427</v>
       </c>
       <c r="H482">
         <v>1.7</v>
@@ -17132,10 +17222,10 @@
         <v>1258</v>
       </c>
       <c r="F483" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G483" t="s">
-        <v>1397</v>
+        <v>1428</v>
       </c>
       <c r="H483">
         <v>2.1</v>
@@ -17158,10 +17248,10 @@
         <v>1258</v>
       </c>
       <c r="F484" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="G484" t="s">
-        <v>1398</v>
+        <v>1429</v>
       </c>
       <c r="H484">
         <v>2.5</v>
@@ -17184,10 +17274,10 @@
         <v>1260</v>
       </c>
       <c r="F485" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G485" t="s">
-        <v>1399</v>
+        <v>1430</v>
       </c>
       <c r="H485">
         <v>-2.2</v>
@@ -17210,10 +17300,10 @@
         <v>1258</v>
       </c>
       <c r="F486" t="s">
-        <v>1261</v>
+        <v>1296</v>
       </c>
       <c r="G486" t="s">
-        <v>1400</v>
+        <v>1431</v>
       </c>
       <c r="H486">
         <v>1.5</v>
@@ -17236,10 +17326,10 @@
         <v>1259</v>
       </c>
       <c r="F487" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G487" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H487">
         <v>0</v>
@@ -17262,10 +17352,10 @@
         <v>1260</v>
       </c>
       <c r="F488" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G488" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H488">
         <v>-1.7</v>
@@ -17288,10 +17378,10 @@
         <v>1259</v>
       </c>
       <c r="F489" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G489" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H489">
         <v>0</v>
@@ -17314,10 +17404,10 @@
         <v>1258</v>
       </c>
       <c r="F490" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G490" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H490">
         <v>2.1</v>
@@ -17340,10 +17430,10 @@
         <v>1258</v>
       </c>
       <c r="F491" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G491" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H491">
         <v>0.8</v>
@@ -17366,10 +17456,10 @@
         <v>1260</v>
       </c>
       <c r="F492" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G492" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H492">
         <v>-1.7</v>
@@ -17392,10 +17482,10 @@
         <v>1259</v>
       </c>
       <c r="F493" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G493" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H493">
         <v>0</v>
@@ -17418,10 +17508,10 @@
         <v>1258</v>
       </c>
       <c r="F494" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G494" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H494">
         <v>2.9</v>
@@ -17444,10 +17534,10 @@
         <v>1258</v>
       </c>
       <c r="F495" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G495" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H495">
         <v>2.6</v>
@@ -17470,10 +17560,10 @@
         <v>1258</v>
       </c>
       <c r="F496" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G496" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H496">
         <v>1.1</v>
@@ -17496,10 +17586,10 @@
         <v>1260</v>
       </c>
       <c r="F497" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G497" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H497">
         <v>-2.3</v>
@@ -17522,10 +17612,10 @@
         <v>1260</v>
       </c>
       <c r="F498" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G498" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H498">
         <v>-1.6</v>
@@ -17548,10 +17638,10 @@
         <v>1260</v>
       </c>
       <c r="F499" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G499" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H499">
         <v>-2.2</v>
@@ -17574,10 +17664,10 @@
         <v>1260</v>
       </c>
       <c r="F500" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G500" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H500">
         <v>-0.5</v>
@@ -17600,10 +17690,10 @@
         <v>1258</v>
       </c>
       <c r="F501" t="s">
-        <v>1263</v>
+        <v>1305</v>
       </c>
       <c r="G501" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H501">
         <v>1.8</v>
@@ -17626,10 +17716,10 @@
         <v>1259</v>
       </c>
       <c r="F502" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G502" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H502">
         <v>0</v>
@@ -17652,10 +17742,10 @@
         <v>1260</v>
       </c>
       <c r="F503" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G503" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H503">
         <v>-1.2</v>
@@ -17678,10 +17768,10 @@
         <v>1260</v>
       </c>
       <c r="F504" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G504" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H504">
         <v>0</v>
@@ -17704,10 +17794,10 @@
         <v>1260</v>
       </c>
       <c r="F505" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G505" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H505">
         <v>-1.9</v>
@@ -17730,10 +17820,10 @@
         <v>1260</v>
       </c>
       <c r="F506" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G506" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H506">
         <v>-3.2</v>
@@ -17756,10 +17846,10 @@
         <v>1260</v>
       </c>
       <c r="F507" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G507" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H507">
         <v>-0.6</v>
@@ -17782,10 +17872,10 @@
         <v>1258</v>
       </c>
       <c r="F508" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="G508" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H508">
         <v>2</v>
@@ -17808,10 +17898,10 @@
         <v>1260</v>
       </c>
       <c r="F509" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G509" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H509">
         <v>-1.1</v>
@@ -17834,10 +17924,10 @@
         <v>1258</v>
       </c>
       <c r="F510" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G510" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H510">
         <v>1.8</v>
@@ -17860,10 +17950,10 @@
         <v>1260</v>
       </c>
       <c r="F511" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G511" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H511">
         <v>-2.1</v>
@@ -17886,10 +17976,10 @@
         <v>1260</v>
       </c>
       <c r="F512" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G512" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H512">
         <v>-1.9</v>
@@ -17912,10 +18002,10 @@
         <v>1258</v>
       </c>
       <c r="F513" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G513" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H513">
         <v>0.2</v>
@@ -17938,10 +18028,10 @@
         <v>1259</v>
       </c>
       <c r="F514" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="G514" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H514">
         <v>0</v>
@@ -17964,10 +18054,10 @@
         <v>1259</v>
       </c>
       <c r="F515" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G515" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H515">
         <v>0</v>
@@ -17990,10 +18080,10 @@
         <v>1259</v>
       </c>
       <c r="F516" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G516" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H516">
         <v>0</v>
@@ -18016,10 +18106,10 @@
         <v>1259</v>
       </c>
       <c r="F517" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G517" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H517">
         <v>0</v>
@@ -18042,10 +18132,10 @@
         <v>1258</v>
       </c>
       <c r="F518" t="s">
-        <v>1263</v>
+        <v>1305</v>
       </c>
       <c r="G518" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H518">
         <v>0.9</v>
@@ -18068,10 +18158,10 @@
         <v>1258</v>
       </c>
       <c r="F519" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G519" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H519">
         <v>1.5</v>
@@ -18094,10 +18184,10 @@
         <v>1259</v>
       </c>
       <c r="F520" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="G520" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H520">
         <v>0</v>
@@ -18120,10 +18210,10 @@
         <v>1258</v>
       </c>
       <c r="F521" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G521" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H521">
         <v>1.8</v>
@@ -18146,10 +18236,10 @@
         <v>1259</v>
       </c>
       <c r="F522" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G522" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -18172,10 +18262,10 @@
         <v>1260</v>
       </c>
       <c r="F523" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G523" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H523">
         <v>-2.1</v>
@@ -18198,10 +18288,10 @@
         <v>1260</v>
       </c>
       <c r="F524" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G524" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H524">
         <v>-1.5</v>
@@ -18224,10 +18314,10 @@
         <v>1260</v>
       </c>
       <c r="F525" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G525" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H525">
         <v>-2.4</v>
@@ -18250,10 +18340,10 @@
         <v>1259</v>
       </c>
       <c r="F526" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G526" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H526">
         <v>0</v>
@@ -18276,10 +18366,10 @@
         <v>1259</v>
       </c>
       <c r="F527" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G527" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H527">
         <v>0</v>
@@ -18302,10 +18392,10 @@
         <v>1260</v>
       </c>
       <c r="F528" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G528" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H528">
         <v>-1.7</v>
@@ -18328,10 +18418,10 @@
         <v>1260</v>
       </c>
       <c r="F529" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G529" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H529">
         <v>-2.6</v>
@@ -18354,10 +18444,10 @@
         <v>1258</v>
       </c>
       <c r="F530" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G530" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H530">
         <v>2.4</v>
@@ -18380,10 +18470,10 @@
         <v>1260</v>
       </c>
       <c r="F531" t="s">
-        <v>1269</v>
+        <v>1305</v>
       </c>
       <c r="G531" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H531">
         <v>-2.4</v>
@@ -18406,10 +18496,10 @@
         <v>1259</v>
       </c>
       <c r="F532" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G532" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H532">
         <v>0</v>
@@ -18432,10 +18522,10 @@
         <v>1260</v>
       </c>
       <c r="F533" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
       <c r="G533" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H533">
         <v>-1.6</v>
@@ -18458,10 +18548,10 @@
         <v>1259</v>
       </c>
       <c r="F534" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G534" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H534">
         <v>0</v>
@@ -18484,10 +18574,10 @@
         <v>1260</v>
       </c>
       <c r="F535" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G535" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H535">
         <v>-2.7</v>
@@ -18510,10 +18600,10 @@
         <v>1260</v>
       </c>
       <c r="F536" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G536" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H536">
         <v>-2.4</v>
@@ -18536,10 +18626,10 @@
         <v>1259</v>
       </c>
       <c r="F537" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G537" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H537">
         <v>0</v>
@@ -18562,10 +18652,10 @@
         <v>1258</v>
       </c>
       <c r="F538" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G538" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H538">
         <v>3</v>
@@ -18588,10 +18678,10 @@
         <v>1260</v>
       </c>
       <c r="F539" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G539" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H539">
         <v>-1.5</v>
@@ -18614,10 +18704,10 @@
         <v>1260</v>
       </c>
       <c r="F540" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G540" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H540">
         <v>-0.6</v>
@@ -18640,10 +18730,10 @@
         <v>1259</v>
       </c>
       <c r="F541" t="s">
-        <v>1268</v>
+        <v>1305</v>
       </c>
       <c r="G541" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H541">
         <v>0</v>
@@ -18666,10 +18756,10 @@
         <v>1260</v>
       </c>
       <c r="F542" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G542" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H542">
         <v>-2</v>
@@ -18692,10 +18782,10 @@
         <v>1260</v>
       </c>
       <c r="F543" t="s">
-        <v>1270</v>
+        <v>1305</v>
       </c>
       <c r="G543" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H543">
         <v>-2</v>
@@ -18718,10 +18808,10 @@
         <v>1260</v>
       </c>
       <c r="F544" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G544" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H544">
         <v>-1.4</v>
@@ -18744,10 +18834,10 @@
         <v>1258</v>
       </c>
       <c r="F545" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G545" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H545">
         <v>2.1</v>
@@ -18770,10 +18860,10 @@
         <v>1258</v>
       </c>
       <c r="F546" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="G546" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H546">
         <v>1.4</v>
@@ -18796,10 +18886,10 @@
         <v>1258</v>
       </c>
       <c r="F547" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G547" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H547">
         <v>2.5</v>
@@ -18822,10 +18912,10 @@
         <v>1260</v>
       </c>
       <c r="F548" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G548" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H548">
         <v>-2.4</v>
@@ -18848,10 +18938,10 @@
         <v>1259</v>
       </c>
       <c r="F549" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G549" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H549">
         <v>0</v>
@@ -18874,10 +18964,10 @@
         <v>1259</v>
       </c>
       <c r="F550" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G550" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H550">
         <v>0</v>
@@ -18900,10 +18990,10 @@
         <v>1258</v>
       </c>
       <c r="F551" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G551" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H551">
         <v>0.9</v>
@@ -18926,10 +19016,10 @@
         <v>1259</v>
       </c>
       <c r="F552" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G552" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H552">
         <v>0</v>
@@ -18952,10 +19042,10 @@
         <v>1258</v>
       </c>
       <c r="F553" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G553" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H553">
         <v>2.7</v>
@@ -18978,10 +19068,10 @@
         <v>1258</v>
       </c>
       <c r="F554" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G554" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H554">
         <v>2.4</v>
@@ -19004,10 +19094,10 @@
         <v>1258</v>
       </c>
       <c r="F555" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G555" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H555">
         <v>1.5</v>
@@ -19030,10 +19120,10 @@
         <v>1260</v>
       </c>
       <c r="F556" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G556" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H556">
         <v>-1.1</v>
@@ -19056,10 +19146,10 @@
         <v>1259</v>
       </c>
       <c r="F557" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G557" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H557">
         <v>0</v>
@@ -19082,10 +19172,10 @@
         <v>1260</v>
       </c>
       <c r="F558" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G558" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H558">
         <v>-1.9</v>
@@ -19108,10 +19198,10 @@
         <v>1258</v>
       </c>
       <c r="F559" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G559" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H559">
         <v>1.4</v>
@@ -19134,10 +19224,10 @@
         <v>1260</v>
       </c>
       <c r="F560" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G560" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H560">
         <v>-2.4</v>
@@ -19160,10 +19250,10 @@
         <v>1259</v>
       </c>
       <c r="F561" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G561" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H561">
         <v>0</v>
@@ -19186,10 +19276,10 @@
         <v>1260</v>
       </c>
       <c r="F562" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G562" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H562">
         <v>-1.6</v>
@@ -19212,10 +19302,10 @@
         <v>1260</v>
       </c>
       <c r="F563" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G563" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H563">
         <v>-1.3</v>
@@ -19238,10 +19328,10 @@
         <v>1258</v>
       </c>
       <c r="F564" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G564" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H564">
         <v>2.6</v>
@@ -19264,10 +19354,10 @@
         <v>1259</v>
       </c>
       <c r="F565" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G565" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H565">
         <v>0</v>
@@ -19290,10 +19380,10 @@
         <v>1259</v>
       </c>
       <c r="F566" t="s">
-        <v>1263</v>
+        <v>1305</v>
       </c>
       <c r="G566" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H566">
         <v>0</v>
@@ -19316,10 +19406,10 @@
         <v>1260</v>
       </c>
       <c r="F567" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G567" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H567">
         <v>-1.8</v>
@@ -19342,10 +19432,10 @@
         <v>1258</v>
       </c>
       <c r="F568" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G568" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H568">
         <v>1.7</v>
@@ -19368,10 +19458,10 @@
         <v>1258</v>
       </c>
       <c r="F569" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G569" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H569">
         <v>2.9</v>
@@ -19394,10 +19484,10 @@
         <v>1260</v>
       </c>
       <c r="F570" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G570" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H570">
         <v>-1.3</v>
@@ -19420,10 +19510,10 @@
         <v>1258</v>
       </c>
       <c r="F571" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G571" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H571">
         <v>0.5</v>
@@ -19446,10 +19536,10 @@
         <v>1260</v>
       </c>
       <c r="F572" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G572" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H572">
         <v>-0.9</v>
@@ -19472,10 +19562,10 @@
         <v>1259</v>
       </c>
       <c r="F573" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G573" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H573">
         <v>0</v>
@@ -19498,10 +19588,10 @@
         <v>1258</v>
       </c>
       <c r="F574" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G574" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H574">
         <v>1.6</v>
@@ -19524,10 +19614,10 @@
         <v>1258</v>
       </c>
       <c r="F575" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G575" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H575">
         <v>1.9</v>
@@ -19550,10 +19640,10 @@
         <v>1259</v>
       </c>
       <c r="F576" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G576" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H576">
         <v>0</v>
@@ -19576,10 +19666,10 @@
         <v>1258</v>
       </c>
       <c r="F577" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G577" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H577">
         <v>1.8</v>
@@ -19602,10 +19692,10 @@
         <v>1258</v>
       </c>
       <c r="F578" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G578" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H578">
         <v>2.3</v>
@@ -19628,10 +19718,10 @@
         <v>1259</v>
       </c>
       <c r="F579" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G579" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H579">
         <v>0</v>
@@ -19654,10 +19744,10 @@
         <v>1259</v>
       </c>
       <c r="F580" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G580" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H580">
         <v>0</v>
@@ -19680,10 +19770,10 @@
         <v>1258</v>
       </c>
       <c r="F581" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G581" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H581">
         <v>2</v>
@@ -19706,10 +19796,10 @@
         <v>1260</v>
       </c>
       <c r="F582" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G582" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H582">
         <v>-1.9</v>
@@ -19732,10 +19822,10 @@
         <v>1260</v>
       </c>
       <c r="F583" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G583" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H583">
         <v>-1.6</v>
@@ -19758,10 +19848,10 @@
         <v>1259</v>
       </c>
       <c r="F584" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G584" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H584">
         <v>0</v>
@@ -19784,10 +19874,10 @@
         <v>1259</v>
       </c>
       <c r="F585" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G585" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H585">
         <v>0</v>
@@ -19810,10 +19900,10 @@
         <v>1258</v>
       </c>
       <c r="F586" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G586" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H586">
         <v>2.2</v>
@@ -19836,10 +19926,10 @@
         <v>1259</v>
       </c>
       <c r="F587" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="G587" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H587">
         <v>0</v>
@@ -19862,10 +19952,10 @@
         <v>1260</v>
       </c>
       <c r="F588" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G588" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H588">
         <v>-1.6</v>
@@ -19888,10 +19978,10 @@
         <v>1260</v>
       </c>
       <c r="F589" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G589" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H589">
         <v>-2.1</v>
@@ -19914,10 +20004,10 @@
         <v>1259</v>
       </c>
       <c r="F590" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G590" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H590">
         <v>0</v>
@@ -19940,10 +20030,10 @@
         <v>1260</v>
       </c>
       <c r="F591" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G591" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H591">
         <v>-0.5</v>
@@ -19966,10 +20056,10 @@
         <v>1259</v>
       </c>
       <c r="F592" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G592" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H592">
         <v>0</v>
@@ -19992,10 +20082,10 @@
         <v>1258</v>
       </c>
       <c r="F593" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G593" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H593">
         <v>2.4</v>
@@ -20018,10 +20108,10 @@
         <v>1260</v>
       </c>
       <c r="F594" t="s">
-        <v>1270</v>
+        <v>1305</v>
       </c>
       <c r="G594" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H594">
         <v>-2</v>
@@ -20044,10 +20134,10 @@
         <v>1259</v>
       </c>
       <c r="F595" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G595" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H595">
         <v>0</v>
@@ -20070,10 +20160,10 @@
         <v>1259</v>
       </c>
       <c r="F596" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G596" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H596">
         <v>0</v>
@@ -20096,10 +20186,10 @@
         <v>1260</v>
       </c>
       <c r="F597" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G597" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H597">
         <v>-1.3</v>
@@ -20122,10 +20212,10 @@
         <v>1258</v>
       </c>
       <c r="F598" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G598" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H598">
         <v>2.8</v>
@@ -20148,10 +20238,10 @@
         <v>1259</v>
       </c>
       <c r="F599" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G599" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H599">
         <v>0</v>
@@ -20174,10 +20264,10 @@
         <v>1258</v>
       </c>
       <c r="F600" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G600" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H600">
         <v>2</v>
@@ -20200,10 +20290,10 @@
         <v>1260</v>
       </c>
       <c r="F601" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G601" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H601">
         <v>-1.6</v>
@@ -20226,10 +20316,10 @@
         <v>1259</v>
       </c>
       <c r="F602" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G602" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H602">
         <v>0</v>
@@ -20252,10 +20342,10 @@
         <v>1258</v>
       </c>
       <c r="F603" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="G603" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H603">
         <v>1.8</v>
@@ -20278,10 +20368,10 @@
         <v>1260</v>
       </c>
       <c r="F604" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G604" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H604">
         <v>-1.5</v>
@@ -20304,10 +20394,10 @@
         <v>1259</v>
       </c>
       <c r="F605" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G605" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H605">
         <v>0</v>
@@ -20330,10 +20420,10 @@
         <v>1259</v>
       </c>
       <c r="F606" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G606" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H606">
         <v>0</v>
@@ -20356,10 +20446,10 @@
         <v>1260</v>
       </c>
       <c r="F607" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G607" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H607">
         <v>-3</v>
@@ -20382,10 +20472,10 @@
         <v>1260</v>
       </c>
       <c r="F608" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G608" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H608">
         <v>-2</v>
@@ -20408,10 +20498,10 @@
         <v>1258</v>
       </c>
       <c r="F609" t="s">
-        <v>1262</v>
+        <v>1305</v>
       </c>
       <c r="G609" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H609">
         <v>2.7</v>
@@ -20434,10 +20524,10 @@
         <v>1259</v>
       </c>
       <c r="F610" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G610" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H610">
         <v>0</v>
@@ -20460,10 +20550,10 @@
         <v>1258</v>
       </c>
       <c r="F611" t="s">
-        <v>1267</v>
+        <v>1305</v>
       </c>
       <c r="G611" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H611">
         <v>2</v>
@@ -20486,10 +20576,10 @@
         <v>1259</v>
       </c>
       <c r="F612" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G612" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H612">
         <v>0</v>
@@ -20512,10 +20602,10 @@
         <v>1259</v>
       </c>
       <c r="F613" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G613" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H613">
         <v>0</v>
@@ -20538,10 +20628,10 @@
         <v>1259</v>
       </c>
       <c r="F614" t="s">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="G614" t="s">
-        <v>1401</v>
+        <v>1432</v>
       </c>
       <c r="H614">
         <v>0</v>
@@ -20564,10 +20654,10 @@
         <v>1259</v>
       </c>
       <c r="F615" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G615" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H615">
         <v>0</v>
@@ -20590,10 +20680,10 @@
         <v>1259</v>
       </c>
       <c r="F616" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G616" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H616">
         <v>0</v>
@@ -20616,10 +20706,10 @@
         <v>1259</v>
       </c>
       <c r="F617" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G617" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H617">
         <v>0</v>
@@ -20642,10 +20732,10 @@
         <v>1259</v>
       </c>
       <c r="F618" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G618" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H618">
         <v>0</v>
@@ -20668,10 +20758,10 @@
         <v>1260</v>
       </c>
       <c r="F619" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G619" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H619">
         <v>-1.6</v>
@@ -20694,10 +20784,10 @@
         <v>1259</v>
       </c>
       <c r="F620" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G620" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H620">
         <v>0</v>
@@ -20720,10 +20810,10 @@
         <v>1260</v>
       </c>
       <c r="F621" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G621" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H621">
         <v>-1.9</v>
@@ -20746,10 +20836,10 @@
         <v>1258</v>
       </c>
       <c r="F622" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G622" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H622">
         <v>2.4</v>
@@ -20772,10 +20862,10 @@
         <v>1260</v>
       </c>
       <c r="F623" t="s">
-        <v>1266</v>
+        <v>1305</v>
       </c>
       <c r="G623" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H623">
         <v>-2.6</v>
@@ -20798,10 +20888,10 @@
         <v>1259</v>
       </c>
       <c r="F624" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G624" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H624">
         <v>0</v>
@@ -20824,10 +20914,10 @@
         <v>1259</v>
       </c>
       <c r="F625" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G625" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H625">
         <v>0</v>
@@ -20850,10 +20940,10 @@
         <v>1260</v>
       </c>
       <c r="F626" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="G626" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H626">
         <v>-1.8</v>
@@ -20876,10 +20966,10 @@
         <v>1259</v>
       </c>
       <c r="F627" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G627" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H627">
         <v>0</v>
@@ -20902,10 +20992,10 @@
         <v>1259</v>
       </c>
       <c r="F628" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G628" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H628">
         <v>0</v>
@@ -20928,10 +21018,10 @@
         <v>1259</v>
       </c>
       <c r="F629" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G629" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H629">
         <v>0</v>
@@ -20954,10 +21044,10 @@
         <v>1259</v>
       </c>
       <c r="F630" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G630" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H630">
         <v>0</v>
@@ -20980,10 +21070,10 @@
         <v>1259</v>
       </c>
       <c r="F631" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="G631" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
       <c r="H631">
         <v>0</v>
